--- a/report-2026-06-05.xlsx
+++ b/report-2026-06-05.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="839">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-05T00:05:00+05:30</t>
+    <t>Generated 2026-06-05T02:37:03+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-05T00:04:32+05:30 (27s ago)</t>
+    <t>2026-06-05T02:35:03+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>22</t>
+    <t>1</t>
   </si>
   <si>
     <t>Last error</t>
@@ -2179,10 +2179,358 @@
     <t>00:04:32.916</t>
   </si>
   <si>
+    <t>2026-06-05T00:07:02.682108+05:30</t>
+  </si>
+  <si>
+    <t>00:07:02.682</t>
+  </si>
+  <si>
+    <t>2026-06-05T00:09:32.7430951+05:30</t>
+  </si>
+  <si>
+    <t>00:09:32.743</t>
+  </si>
+  <si>
+    <t>2026-06-05T00:12:03.6538945+05:30</t>
+  </si>
+  <si>
+    <t>00:12:03.653</t>
+  </si>
+  <si>
+    <t>2026-06-05T00:14:33.1652939+05:30</t>
+  </si>
+  <si>
+    <t>00:14:33.165</t>
+  </si>
+  <si>
+    <t>2026-06-05T00:17:01.4772977+05:30</t>
+  </si>
+  <si>
+    <t>00:17:01.477</t>
+  </si>
+  <si>
+    <t>2026-06-05T00:22:02.6996987+05:30</t>
+  </si>
+  <si>
+    <t>00:22:02.699</t>
+  </si>
+  <si>
+    <t>2026-06-05T00:24:33.7348311+05:30</t>
+  </si>
+  <si>
+    <t>00:24:33.734</t>
+  </si>
+  <si>
+    <t>2026-06-05T00:27:02.8526079+05:30</t>
+  </si>
+  <si>
+    <t>00:27:02.852</t>
+  </si>
+  <si>
+    <t>2026-06-05T00:29:32.8134668+05:30</t>
+  </si>
+  <si>
+    <t>00:29:32.813</t>
+  </si>
+  <si>
+    <t>2026-06-05T00:32:03.2331724+05:30</t>
+  </si>
+  <si>
+    <t>00:32:03.233</t>
+  </si>
+  <si>
+    <t>2026-06-05T00:34:32.6876041+05:30</t>
+  </si>
+  <si>
+    <t>00:34:32.687</t>
+  </si>
+  <si>
+    <t>2026-06-05T00:37:02.6923226+05:30</t>
+  </si>
+  <si>
+    <t>00:37:02.692</t>
+  </si>
+  <si>
+    <t>2026-06-05T00:39:32.6895814+05:30</t>
+  </si>
+  <si>
+    <t>00:39:32.689</t>
+  </si>
+  <si>
+    <t>2026-06-05T00:42:03.2305731+05:30</t>
+  </si>
+  <si>
+    <t>00:42:03.230</t>
+  </si>
+  <si>
+    <t>2026-06-05T00:44:32.7823025+05:30</t>
+  </si>
+  <si>
+    <t>00:44:32.782</t>
+  </si>
+  <si>
+    <t>2026-06-05T00:47:02.7277371+05:30</t>
+  </si>
+  <si>
+    <t>00:47:02.727</t>
+  </si>
+  <si>
+    <t>2026-06-05T00:49:32.6718757+05:30</t>
+  </si>
+  <si>
+    <t>00:49:32.671</t>
+  </si>
+  <si>
+    <t>2026-06-05T00:52:02.6987242+05:30</t>
+  </si>
+  <si>
+    <t>00:52:02.698</t>
+  </si>
+  <si>
+    <t>2026-06-05T00:54:33.1283526+05:30</t>
+  </si>
+  <si>
+    <t>00:54:33.128</t>
+  </si>
+  <si>
+    <t>2026-06-05T00:57:02.6363655+05:30</t>
+  </si>
+  <si>
+    <t>00:57:02.636</t>
+  </si>
+  <si>
+    <t>2026-06-05T00:59:32.7455309+05:30</t>
+  </si>
+  <si>
+    <t>00:59:32.745</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:02:02.8506093+05:30</t>
+  </si>
+  <si>
+    <t>01:02:02.850</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:04:32.7566888+05:30</t>
+  </si>
+  <si>
+    <t>01:04:32.756</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:07:02.8867735+05:30</t>
+  </si>
+  <si>
+    <t>01:07:02.886</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:09:32.6816217+05:30</t>
+  </si>
+  <si>
+    <t>01:09:32.681</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:12:02.7296268+05:30</t>
+  </si>
+  <si>
+    <t>01:12:02.729</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:14:32.6346442+05:30</t>
+  </si>
+  <si>
+    <t>01:14:32.634</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:17:02.7638328+05:30</t>
+  </si>
+  <si>
+    <t>01:17:02.763</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:19:32.7863266+05:30</t>
+  </si>
+  <si>
+    <t>01:19:32.786</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:22:02.7561361+05:30</t>
+  </si>
+  <si>
+    <t>01:22:02.756</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:24:32.6497083+05:30</t>
+  </si>
+  <si>
+    <t>01:24:32.649</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:27:02.7656271+05:30</t>
+  </si>
+  <si>
+    <t>01:27:02.765</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:29:32.843618+05:30</t>
+  </si>
+  <si>
+    <t>01:29:32.843</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:32:02.7154467+05:30</t>
+  </si>
+  <si>
+    <t>01:32:02.715</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:34:32.5760866+05:30</t>
+  </si>
+  <si>
+    <t>01:34:32.576</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:37:02.6561512+05:30</t>
+  </si>
+  <si>
+    <t>01:37:02.656</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:39:32.6894945+05:30</t>
+  </si>
+  <si>
+    <t>01:39:32.689</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:42:02.5812192+05:30</t>
+  </si>
+  <si>
+    <t>01:42:02.581</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:44:31.4809203+05:30</t>
+  </si>
+  <si>
+    <t>01:44:31.480</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:47:01.4719465+05:30</t>
+  </si>
+  <si>
+    <t>01:47:01.471</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:52:02.7307505+05:30</t>
+  </si>
+  <si>
+    <t>01:52:02.730</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:54:32.6608948+05:30</t>
+  </si>
+  <si>
+    <t>01:54:32.660</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:57:02.631462+05:30</t>
+  </si>
+  <si>
+    <t>01:57:02.631</t>
+  </si>
+  <si>
+    <t>2026-06-05T01:59:32.7296423+05:30</t>
+  </si>
+  <si>
+    <t>01:59:32.729</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:02:02.6953795+05:30</t>
+  </si>
+  <si>
+    <t>02:02:02.695</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:04:32.6159543+05:30</t>
+  </si>
+  <si>
+    <t>02:04:32.615</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:07:02.7124893+05:30</t>
+  </si>
+  <si>
+    <t>02:07:02.712</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:09:32.7239091+05:30</t>
+  </si>
+  <si>
+    <t>02:09:32.723</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:12:02.7892506+05:30</t>
+  </si>
+  <si>
+    <t>02:12:02.789</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:14:32.7311725+05:30</t>
+  </si>
+  <si>
+    <t>02:14:32.731</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:17:02.6843751+05:30</t>
+  </si>
+  <si>
+    <t>02:17:02.684</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:19:33.800804+05:30</t>
+  </si>
+  <si>
+    <t>02:19:33.800</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:22:02.777983+05:30</t>
+  </si>
+  <si>
+    <t>02:22:02.777</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:24:32.7169137+05:30</t>
+  </si>
+  <si>
+    <t>02:24:32.716</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:27:02.7558024+05:30</t>
+  </si>
+  <si>
+    <t>02:27:02.755</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:29:32.6860433+05:30</t>
+  </si>
+  <si>
+    <t>02:29:32.686</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:32:02.8513106+05:30</t>
+  </si>
+  <si>
+    <t>02:32:02.851</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:34:32.8944865+05:30</t>
+  </si>
+  <si>
+    <t>02:34:32.894</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-05T00:05:00+05:30</t>
+    <t>2026-06-05T02:37:03+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -2737,7 +3085,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.54</t>
+          <t>10.0.55</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2777,12 +3125,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 53m 13s</t>
+          <t>0h 2m 15s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-04 23:11:46</t>
+          <t>2026-06-05 02:34:48</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -2792,12 +3140,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-04 23:11:46</t>
+          <t>2026-06-05 02:34:48</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>13h 3m 40s</t>
+          <t>0h 0m 15s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -2807,44 +3155,44 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>00:05:00</t>
+          <t>02:37:03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Puneets-MacBook-Air.local-esHl</t>
+          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Puneets-MacBook-Air.local</t>
+          <t>PuneetU-EB6LMJD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>192.168.0.156</t>
+          <t>192.168.0.128</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.247.40.101</t>
+          <t>103.117.15.39</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>darwin</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>arm64</t>
+          <t>amd64</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.0</t>
+          <t>10.0.55</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2854,27 +3202,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>websocket</t>
+          <t>self</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>degraded</t>
+          <t>good</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>15150.5</t>
+          <t>91587.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2884,27 +3232,27 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-03 10:39:05</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Jun 2 05:41 PM</t>
+          <t>Jun 4 07:08 PM</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-03 10:39:05</t>
+          <t>2026-06-05 02:34:48</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>13h 53m 15s</t>
+          <t>0h 0m 0s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -2914,324 +3262,217 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>00:05:00</t>
+          <t>02:37:03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
+          <t>── LATEST GITHUB ELECTION EVENT ──</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PuneetU-EB6LMJD</t>
+          <t/>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>192.168.0.128</t>
+          <t/>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>103.117.15.39</t>
+          <t/>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>windows</t>
+          <t/>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>amd64</t>
+          <t/>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.0.54</t>
+          <t/>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t/>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>self</t>
+          <t/>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t/>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t/>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>485195.5</t>
+          <t/>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>22173</t>
+          <t/>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t/>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t/>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t/>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Jun 4 07:08 PM</t>
+          <t/>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-06-04 23:11:46</t>
+          <t/>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>12h 29m 40s</t>
+          <t/>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t/>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>00:05:00</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>── LATEST GITHUB ELECTION EVENT ──</t>
+          <t>[renewed]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>2026-06-05T02:34:32.8944865+05:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>02:34:32.894</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>renewed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PuneetU-EB6LMJD</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
+        </is>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>renewed</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>[renewed]</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-05T00:04:32.9167105+05:30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>00:04:32.916</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>renewed</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>github</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>PuneetU-EB6LMJD</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>PuneetU-EB6LMJD-cf4a9ce5</t>
-        </is>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>renewed</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5237,6 +5478,2526 @@
         </is>
       </c>
       <c r="G57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>1780600983412</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>00:53:03</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>6CHJ0eEi</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>1780600983476</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>00:53:03</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>6CHJ0eEi</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>1780600984473</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>00:53:04</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>RzLij14W</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>1780600984526</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>00:53:04</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RzLij14W</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>1780600985359</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>00:53:05</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>WqP87hcP</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>1780600985423</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>00:53:05</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>WqP87hcP</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>1780600988764</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>00:53:08</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>rJgWyDtF</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>1780600988824</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>00:53:08</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>rJgWyDtF</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>1780600989395</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>00:53:09</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>dkK1BvP5</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>1780600989507</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>00:53:09</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>dkK1BvP5</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>1780600989571</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>00:53:09</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>a6DGVeY8</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>1780600989635</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>00:53:09</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>a6DGVeY8</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>1780600989748</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>00:53:09</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Qekoeuk5</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>1780600989824</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>00:53:09</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Qekoeuk5</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>1780600989971</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>00:53:09</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>WVKYLvZo</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>1780600990051</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>00:53:10</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>WVKYLvZo</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>1780602314538</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>01:15:14</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>sbaYf3vi</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>1780602314591</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>01:15:14</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>sbaYf3vi</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>1780602315163</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>01:15:15</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>5OyAEk4n</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>1780602315222</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>01:15:15</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>5OyAEk4n</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>1780602315761</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>01:15:15</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>bGHa8X7U</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>1780602315809</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>01:15:15</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>bGHa8X7U</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>1780602316179</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>01:15:16</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>MeA77Mb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>1780602316239</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>01:15:16</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>MeA77Mb4</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>1780602316670</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>01:15:16</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>xQDOougo</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>1780602316724</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>01:15:16</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>xQDOougo</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>1780602316877</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>01:15:16</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>3Geiudxi</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>1780602316944</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>01:15:16</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>3Geiudxi</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>1780602317071</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>01:15:17</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>dAQn8FRd</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>1780602317129</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>01:15:17</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>dAQn8FRd</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>1780602317284</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>01:15:17</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>6Ja8nHER</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>1780602317340</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>01:15:17</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>6Ja8nHER</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>1780602318396</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>01:15:18</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>dtYELs8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>1780602318451</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>01:15:18</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>dtYELs8b</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>1780602551279</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>01:19:11</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>XxI25DXA</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>1780602551376</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>01:19:11</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>XxI25DXA</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>1780602552154</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>01:19:12</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>RBioRFX1</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>1780602552366</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>01:19:12</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>RBioRFX1</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>1780603421256</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>01:33:41</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>ao8u0KdF</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>1780603421318</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>01:33:41</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ao8u0KdF</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>1780603422051</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>01:33:42</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>tAfALa7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>1780603422110</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>01:33:42</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>tAfALa7d</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>1780603687903</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>01:38:07</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>daOQtFvj</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>1780603687990</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>01:38:07</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>daOQtFvj</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>1780603688901</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>01:38:08</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>HugAn2KR</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>1780603688976</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>01:38:08</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>HugAn2KR</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>1780603690096</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>01:38:10</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>ykKNCNw4</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>1780603690156</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>01:38:10</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>ykKNCNw4</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>1780603706920</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>01:38:26</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>C8GnOxIx</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>1780603707027</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>01:38:27</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>C8GnOxIx</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>1780603707643</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>01:38:27</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>7dlIIYyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>1780603707704</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>01:38:27</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>7dlIIYyz</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>1780603994457</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>01:43:14</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Z8T91jUc</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>1780603994535</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>01:43:14</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Z8T91jUc</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>1780603995258</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>01:43:15</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>H7K4E8Zh</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>1780603995324</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>01:43:15</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>H7K4E8Zh</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>1780604793200</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>01:56:33</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Yw93ugvJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>1780604793267</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>01:56:33</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Yw93ugvJ</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>1780604793835</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>01:56:33</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>12JoXvNw</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>1780604793882</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>01:56:33</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>12JoXvNw</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>1780605557262</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>02:09:17</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>nPTee7kP</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>1780605557316</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>02:09:17</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>nPTee7kP</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>1780605557829</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>02:09:17</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>zGBeDcYc</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>1780605557883</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>02:09:17</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>zGBeDcYc</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>1780605763423</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>02:12:43</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>TW0gTJMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>1780605763474</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>02:12:43</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>TW0gTJMG</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>1780605765035</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>02:12:45</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>v6xUvEar</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>1780605765112</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>02:12:45</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>v6xUvEar</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>1780605765854</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>02:12:45</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>KJua7Zy8</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>1780605765903</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>02:12:45</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>KJua7Zy8</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>1780605771601</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>02:12:51</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>QZF6Hq3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>1780605771651</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>02:12:51</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>QZF6Hq3d</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -18156,18 +20917,2222 @@
         <v>43</v>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" s="4">
+        <v>336</v>
+      </c>
+      <c r="B353" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="C353" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D353" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="E353" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F353" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G353" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H353" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I353" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J353" s="4">
+        <v>0</v>
+      </c>
+      <c r="K353" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L353" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="354">
-      <c r="A354" t="s">
-        <v>720</v>
-      </c>
-      <c r="B354" t="s">
-        <v>721</v>
-      </c>
-      <c r="D354" t="s">
+      <c r="A354" s="4">
+        <v>337</v>
+      </c>
+      <c r="B354" s="4" t="s">
         <v>722</v>
       </c>
-      <c r="E354">
-        <v>335</v>
+      <c r="C354" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D354" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="E354" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F354" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G354" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H354" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I354" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J354" s="4">
+        <v>0</v>
+      </c>
+      <c r="K354" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L354" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="4">
+        <v>338</v>
+      </c>
+      <c r="B355" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="C355" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D355" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="E355" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F355" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G355" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H355" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I355" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J355" s="4">
+        <v>0</v>
+      </c>
+      <c r="K355" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L355" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="4">
+        <v>339</v>
+      </c>
+      <c r="B356" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="C356" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D356" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="E356" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F356" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G356" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H356" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I356" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J356" s="4">
+        <v>0</v>
+      </c>
+      <c r="K356" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L356" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="3">
+        <v>340</v>
+      </c>
+      <c r="B357" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="C357" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="D357" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="E357" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F357" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G357" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H357" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I357" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J357" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K357" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L357" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="4">
+        <v>341</v>
+      </c>
+      <c r="B358" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="C358" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D358" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="E358" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F358" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G358" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H358" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I358" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J358" s="4">
+        <v>0</v>
+      </c>
+      <c r="K358" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L358" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="4">
+        <v>342</v>
+      </c>
+      <c r="B359" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="C359" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D359" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="E359" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F359" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G359" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H359" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I359" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J359" s="4">
+        <v>0</v>
+      </c>
+      <c r="K359" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L359" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="4">
+        <v>343</v>
+      </c>
+      <c r="B360" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="C360" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D360" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="E360" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F360" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G360" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H360" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I360" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J360" s="4">
+        <v>0</v>
+      </c>
+      <c r="K360" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L360" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="4">
+        <v>344</v>
+      </c>
+      <c r="B361" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="C361" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D361" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="E361" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F361" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G361" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H361" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I361" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J361" s="4">
+        <v>0</v>
+      </c>
+      <c r="K361" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L361" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="4">
+        <v>345</v>
+      </c>
+      <c r="B362" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="C362" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D362" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="E362" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F362" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G362" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H362" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I362" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J362" s="4">
+        <v>0</v>
+      </c>
+      <c r="K362" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L362" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="4">
+        <v>346</v>
+      </c>
+      <c r="B363" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="C363" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D363" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="E363" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F363" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G363" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H363" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I363" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J363" s="4">
+        <v>0</v>
+      </c>
+      <c r="K363" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L363" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="4">
+        <v>347</v>
+      </c>
+      <c r="B364" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="C364" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D364" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="E364" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F364" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G364" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H364" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I364" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J364" s="4">
+        <v>0</v>
+      </c>
+      <c r="K364" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L364" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="4">
+        <v>348</v>
+      </c>
+      <c r="B365" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="C365" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D365" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="E365" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F365" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G365" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H365" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I365" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J365" s="4">
+        <v>0</v>
+      </c>
+      <c r="K365" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L365" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="4">
+        <v>349</v>
+      </c>
+      <c r="B366" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="C366" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D366" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="E366" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F366" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G366" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H366" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I366" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J366" s="4">
+        <v>0</v>
+      </c>
+      <c r="K366" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L366" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="4">
+        <v>350</v>
+      </c>
+      <c r="B367" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="C367" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D367" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="E367" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F367" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G367" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H367" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I367" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J367" s="4">
+        <v>0</v>
+      </c>
+      <c r="K367" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L367" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="4">
+        <v>351</v>
+      </c>
+      <c r="B368" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="C368" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D368" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="E368" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F368" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G368" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H368" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I368" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J368" s="4">
+        <v>0</v>
+      </c>
+      <c r="K368" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L368" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="4">
+        <v>352</v>
+      </c>
+      <c r="B369" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="C369" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D369" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="E369" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F369" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G369" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H369" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I369" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J369" s="4">
+        <v>0</v>
+      </c>
+      <c r="K369" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L369" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="4">
+        <v>353</v>
+      </c>
+      <c r="B370" s="4" t="s">
+        <v>754</v>
+      </c>
+      <c r="C370" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D370" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="E370" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F370" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G370" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H370" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I370" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J370" s="4">
+        <v>0</v>
+      </c>
+      <c r="K370" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L370" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="4">
+        <v>354</v>
+      </c>
+      <c r="B371" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="C371" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D371" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="E371" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F371" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G371" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H371" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I371" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J371" s="4">
+        <v>0</v>
+      </c>
+      <c r="K371" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L371" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="4">
+        <v>355</v>
+      </c>
+      <c r="B372" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="C372" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D372" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="E372" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F372" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G372" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H372" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I372" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J372" s="4">
+        <v>0</v>
+      </c>
+      <c r="K372" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L372" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="4">
+        <v>356</v>
+      </c>
+      <c r="B373" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="C373" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D373" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="E373" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F373" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G373" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H373" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I373" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J373" s="4">
+        <v>0</v>
+      </c>
+      <c r="K373" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L373" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="4">
+        <v>357</v>
+      </c>
+      <c r="B374" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="C374" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D374" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="E374" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F374" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G374" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H374" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I374" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J374" s="4">
+        <v>0</v>
+      </c>
+      <c r="K374" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L374" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="4">
+        <v>358</v>
+      </c>
+      <c r="B375" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="C375" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D375" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="E375" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F375" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G375" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H375" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I375" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J375" s="4">
+        <v>0</v>
+      </c>
+      <c r="K375" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L375" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="4">
+        <v>359</v>
+      </c>
+      <c r="B376" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="C376" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D376" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="E376" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F376" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G376" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H376" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I376" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J376" s="4">
+        <v>0</v>
+      </c>
+      <c r="K376" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L376" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="4">
+        <v>360</v>
+      </c>
+      <c r="B377" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="C377" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D377" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="E377" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F377" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G377" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H377" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I377" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J377" s="4">
+        <v>0</v>
+      </c>
+      <c r="K377" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L377" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="4">
+        <v>361</v>
+      </c>
+      <c r="B378" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="C378" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D378" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="E378" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F378" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G378" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H378" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I378" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J378" s="4">
+        <v>0</v>
+      </c>
+      <c r="K378" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L378" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="4">
+        <v>362</v>
+      </c>
+      <c r="B379" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C379" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D379" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="E379" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F379" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G379" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H379" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I379" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J379" s="4">
+        <v>0</v>
+      </c>
+      <c r="K379" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L379" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="4">
+        <v>363</v>
+      </c>
+      <c r="B380" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="C380" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D380" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="E380" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F380" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G380" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H380" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I380" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J380" s="4">
+        <v>0</v>
+      </c>
+      <c r="K380" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L380" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="4">
+        <v>364</v>
+      </c>
+      <c r="B381" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="C381" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D381" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="E381" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F381" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G381" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H381" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I381" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J381" s="4">
+        <v>0</v>
+      </c>
+      <c r="K381" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L381" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="4">
+        <v>365</v>
+      </c>
+      <c r="B382" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="C382" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D382" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="E382" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F382" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G382" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H382" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I382" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J382" s="4">
+        <v>0</v>
+      </c>
+      <c r="K382" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L382" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="4">
+        <v>366</v>
+      </c>
+      <c r="B383" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="C383" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D383" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="E383" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F383" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G383" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H383" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I383" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J383" s="4">
+        <v>0</v>
+      </c>
+      <c r="K383" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L383" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="4">
+        <v>367</v>
+      </c>
+      <c r="B384" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="C384" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D384" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="E384" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F384" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G384" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H384" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I384" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J384" s="4">
+        <v>0</v>
+      </c>
+      <c r="K384" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L384" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="4">
+        <v>368</v>
+      </c>
+      <c r="B385" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="C385" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D385" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="E385" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F385" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G385" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H385" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I385" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J385" s="4">
+        <v>0</v>
+      </c>
+      <c r="K385" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L385" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="4">
+        <v>369</v>
+      </c>
+      <c r="B386" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="C386" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D386" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="E386" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F386" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G386" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H386" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I386" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J386" s="4">
+        <v>0</v>
+      </c>
+      <c r="K386" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L386" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="4">
+        <v>370</v>
+      </c>
+      <c r="B387" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="C387" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D387" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="E387" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F387" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G387" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H387" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I387" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J387" s="4">
+        <v>0</v>
+      </c>
+      <c r="K387" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L387" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="4">
+        <v>371</v>
+      </c>
+      <c r="B388" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="C388" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D388" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="E388" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F388" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G388" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H388" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I388" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J388" s="4">
+        <v>0</v>
+      </c>
+      <c r="K388" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L388" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="4">
+        <v>372</v>
+      </c>
+      <c r="B389" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="C389" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D389" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="E389" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F389" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G389" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H389" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I389" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J389" s="4">
+        <v>0</v>
+      </c>
+      <c r="K389" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L389" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="4">
+        <v>373</v>
+      </c>
+      <c r="B390" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="C390" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D390" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="E390" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F390" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G390" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H390" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I390" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J390" s="4">
+        <v>0</v>
+      </c>
+      <c r="K390" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L390" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="3">
+        <v>374</v>
+      </c>
+      <c r="B391" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="C391" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="D391" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="E391" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F391" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G391" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H391" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I391" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J391" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K391" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L391" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="3">
+        <v>375</v>
+      </c>
+      <c r="B392" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="C392" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="D392" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="E392" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F392" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G392" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H392" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I392" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J392" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K392" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L392" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="4">
+        <v>376</v>
+      </c>
+      <c r="B393" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="C393" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D393" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="E393" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F393" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G393" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H393" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I393" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J393" s="4">
+        <v>0</v>
+      </c>
+      <c r="K393" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L393" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="4">
+        <v>377</v>
+      </c>
+      <c r="B394" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="C394" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D394" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="E394" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F394" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G394" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H394" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I394" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J394" s="4">
+        <v>0</v>
+      </c>
+      <c r="K394" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L394" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="4">
+        <v>378</v>
+      </c>
+      <c r="B395" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="C395" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D395" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="E395" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F395" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G395" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H395" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I395" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J395" s="4">
+        <v>0</v>
+      </c>
+      <c r="K395" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L395" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="4">
+        <v>379</v>
+      </c>
+      <c r="B396" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="C396" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D396" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="E396" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F396" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G396" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H396" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I396" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J396" s="4">
+        <v>0</v>
+      </c>
+      <c r="K396" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L396" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="4">
+        <v>380</v>
+      </c>
+      <c r="B397" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="C397" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D397" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="E397" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F397" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G397" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H397" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I397" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J397" s="4">
+        <v>0</v>
+      </c>
+      <c r="K397" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L397" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="4">
+        <v>381</v>
+      </c>
+      <c r="B398" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="C398" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D398" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="E398" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F398" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G398" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H398" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I398" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J398" s="4">
+        <v>0</v>
+      </c>
+      <c r="K398" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L398" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="4">
+        <v>382</v>
+      </c>
+      <c r="B399" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="C399" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D399" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="E399" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F399" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G399" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H399" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I399" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J399" s="4">
+        <v>0</v>
+      </c>
+      <c r="K399" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L399" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="4">
+        <v>383</v>
+      </c>
+      <c r="B400" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="C400" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D400" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="E400" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F400" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G400" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H400" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I400" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J400" s="4">
+        <v>0</v>
+      </c>
+      <c r="K400" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L400" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="4">
+        <v>384</v>
+      </c>
+      <c r="B401" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="C401" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D401" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="E401" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F401" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G401" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H401" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I401" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J401" s="4">
+        <v>0</v>
+      </c>
+      <c r="K401" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L401" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="4">
+        <v>385</v>
+      </c>
+      <c r="B402" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="C402" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D402" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="E402" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F402" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G402" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H402" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I402" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J402" s="4">
+        <v>0</v>
+      </c>
+      <c r="K402" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L402" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="4">
+        <v>386</v>
+      </c>
+      <c r="B403" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="C403" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D403" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="E403" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F403" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G403" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H403" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I403" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J403" s="4">
+        <v>0</v>
+      </c>
+      <c r="K403" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L403" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="4">
+        <v>387</v>
+      </c>
+      <c r="B404" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="C404" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D404" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="E404" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F404" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G404" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H404" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I404" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J404" s="4">
+        <v>0</v>
+      </c>
+      <c r="K404" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L404" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="4">
+        <v>388</v>
+      </c>
+      <c r="B405" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="C405" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D405" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="E405" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F405" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G405" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H405" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I405" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J405" s="4">
+        <v>0</v>
+      </c>
+      <c r="K405" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L405" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="4">
+        <v>389</v>
+      </c>
+      <c r="B406" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="C406" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D406" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="E406" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F406" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G406" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H406" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I406" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J406" s="4">
+        <v>0</v>
+      </c>
+      <c r="K406" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L406" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="4">
+        <v>390</v>
+      </c>
+      <c r="B407" s="4" t="s">
+        <v>828</v>
+      </c>
+      <c r="C407" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D407" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="E407" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F407" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G407" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H407" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I407" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J407" s="4">
+        <v>0</v>
+      </c>
+      <c r="K407" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L407" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="4">
+        <v>391</v>
+      </c>
+      <c r="B408" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="C408" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D408" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="E408" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F408" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G408" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H408" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I408" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J408" s="4">
+        <v>0</v>
+      </c>
+      <c r="K408" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L408" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="4">
+        <v>392</v>
+      </c>
+      <c r="B409" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="C409" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D409" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="E409" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F409" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G409" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H409" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I409" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J409" s="4">
+        <v>0</v>
+      </c>
+      <c r="K409" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L409" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="4">
+        <v>393</v>
+      </c>
+      <c r="B410" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="C410" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D410" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="E410" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F410" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G410" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H410" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I410" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J410" s="4">
+        <v>0</v>
+      </c>
+      <c r="K410" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L410" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="s">
+        <v>836</v>
+      </c>
+      <c r="B412" t="s">
+        <v>837</v>
+      </c>
+      <c r="D412" t="s">
+        <v>838</v>
+      </c>
+      <c r="E412">
+        <v>393</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-05.xlsx
+++ b/report-2026-06-05.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="839">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="917">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-05T02:37:03+05:30</t>
+    <t>Generated 2026-06-05T19:28:52+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-05T02:35:03+05:30 (2m0s ago)</t>
+    <t>2026-06-05T19:26:51+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -2527,10 +2527,244 @@
     <t>02:34:32.894</t>
   </si>
   <si>
+    <t>2026-06-05T02:37:34.9068489+05:30</t>
+  </si>
+  <si>
+    <t>02:37:34.906</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:40:05.1618168+05:30</t>
+  </si>
+  <si>
+    <t>02:40:05.161</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:42:35.1849096+05:30</t>
+  </si>
+  <si>
+    <t>02:42:35.184</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:45:04.9400078+05:30</t>
+  </si>
+  <si>
+    <t>02:45:04.940</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:47:43.8287363+05:30</t>
+  </si>
+  <si>
+    <t>02:47:43.828</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:50:04.9545428+05:30</t>
+  </si>
+  <si>
+    <t>02:50:04.954</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:52:35.0215863+05:30</t>
+  </si>
+  <si>
+    <t>02:52:35.021</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:55:04.9878068+05:30</t>
+  </si>
+  <si>
+    <t>02:55:04.987</t>
+  </si>
+  <si>
+    <t>2026-06-05T02:57:35.071085+05:30</t>
+  </si>
+  <si>
+    <t>02:57:35.071</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:00:05.154798+05:30</t>
+  </si>
+  <si>
+    <t>03:00:05.154</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:02:34.9926986+05:30</t>
+  </si>
+  <si>
+    <t>03:02:34.992</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:05:04.9879623+05:30</t>
+  </si>
+  <si>
+    <t>03:05:04.987</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:07:35.0306512+05:30</t>
+  </si>
+  <si>
+    <t>03:07:35.030</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:10:05.0381657+05:30</t>
+  </si>
+  <si>
+    <t>03:10:05.038</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:12:35.0903573+05:30</t>
+  </si>
+  <si>
+    <t>03:12:35.090</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:15:05.0096252+05:30</t>
+  </si>
+  <si>
+    <t>03:15:05.009</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:17:35.055688+05:30</t>
+  </si>
+  <si>
+    <t>03:17:35.055</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:20:05.0458312+05:30</t>
+  </si>
+  <si>
+    <t>03:20:05.045</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:22:35.0101344+05:30</t>
+  </si>
+  <si>
+    <t>03:22:35.010</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:25:05.0358713+05:30</t>
+  </si>
+  <si>
+    <t>03:25:05.035</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:27:35.0777432+05:30</t>
+  </si>
+  <si>
+    <t>03:27:35.077</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:30:05.0367013+05:30</t>
+  </si>
+  <si>
+    <t>03:30:05.036</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:32:35.0562986+05:30</t>
+  </si>
+  <si>
+    <t>03:32:35.056</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:35:05.0836485+05:30</t>
+  </si>
+  <si>
+    <t>03:35:05.083</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:37:35.1695207+05:30</t>
+  </si>
+  <si>
+    <t>03:37:35.169</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:40:05.0636849+05:30</t>
+  </si>
+  <si>
+    <t>03:40:05.063</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:42:35.055579+05:30</t>
+  </si>
+  <si>
+    <t>03:42:35.055</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:45:05.1407177+05:30</t>
+  </si>
+  <si>
+    <t>03:45:05.140</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:47:35.0121269+05:30</t>
+  </si>
+  <si>
+    <t>03:47:35.012</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:50:04.9810758+05:30</t>
+  </si>
+  <si>
+    <t>03:50:04.981</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:52:35.0832348+05:30</t>
+  </si>
+  <si>
+    <t>03:52:35.083</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:55:05.0128671+05:30</t>
+  </si>
+  <si>
+    <t>03:55:05.012</t>
+  </si>
+  <si>
+    <t>2026-06-05T03:57:35.0112505+05:30</t>
+  </si>
+  <si>
+    <t>03:57:35.011</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:00:05.0614388+05:30</t>
+  </si>
+  <si>
+    <t>04:00:05.061</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:02:33.8458733+05:30</t>
+  </si>
+  <si>
+    <t>04:02:33.845</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:05:03.8307335+05:30</t>
+  </si>
+  <si>
+    <t>04:05:03.830</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:10:03.8297665+05:30</t>
+  </si>
+  <si>
+    <t>04:10:03.829</t>
+  </si>
+  <si>
+    <t>2026-06-05T04:15:03.8462254+05:30</t>
+  </si>
+  <si>
+    <t>04:15:03.846</t>
+  </si>
+  <si>
+    <t>2026-06-05T19:26:51.9335198+05:30</t>
+  </si>
+  <si>
+    <t>19:26:51.933</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-05T02:37:03+05:30</t>
+    <t>2026-06-05T19:28:52+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -3065,7 +3299,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>192.168.0.128</t>
+          <t>192.168.0.111</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3085,7 +3319,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.55</t>
+          <t>10.0.37</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -3125,27 +3359,27 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 15s</t>
+          <t>0h 2m 13s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-05 02:34:48</t>
+          <t>2026-06-05 19:26:38</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Jun 4 07:08 PM</t>
+          <t>Jun 5 07:25 PM</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-05 02:34:48</t>
+          <t>2026-06-05 19:26:38</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0h 0m 15s</t>
+          <t>0h 1m 10s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -3155,7 +3389,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>02:37:03</t>
+          <t>19:28:52</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3406,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>192.168.0.128</t>
+          <t>192.168.0.111</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3192,7 +3426,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.55</t>
+          <t>10.0.37</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -3207,22 +3441,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>stale</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>91587.5</t>
+          <t>119022.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>292</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -3232,7 +3466,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -3242,17 +3476,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Jun 4 07:08 PM</t>
+          <t>Jun 5 07:25 PM</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-05 02:34:48</t>
+          <t>2026-06-05 19:26:38</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0h 0m 0s</t>
+          <t>never</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -3262,7 +3496,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>02:37:03</t>
+          <t>19:28:52</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3615,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-05T02:34:32.8944865+05:30</t>
+          <t>2026-06-05T19:26:51.9335198+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3391,7 +3625,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>02:34:32.894</t>
+          <t>19:26:51.933</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -7998,6 +8232,216 @@
         </is>
       </c>
       <c r="G129" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>1780667826686</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>19:27:06</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>BfuI7ikD</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>1780667826811</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>19:27:06</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>BfuI7ikD</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>1780667827900</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>19:27:07</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>pkht68NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>1780667827976</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>19:27:07</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>pkht68NM</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>1780667828397</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>19:27:08</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>0kiToDYH</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>1780667829471</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>19:27:09</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>0kiToDYH</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -23121,18 +23565,1500 @@
         <v>43</v>
       </c>
     </row>
+    <row r="411">
+      <c r="A411" s="4">
+        <v>394</v>
+      </c>
+      <c r="B411" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="C411" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D411" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="E411" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F411" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G411" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H411" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I411" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J411" s="4">
+        <v>0</v>
+      </c>
+      <c r="K411" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L411" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="412">
-      <c r="A412" t="s">
-        <v>836</v>
-      </c>
-      <c r="B412" t="s">
-        <v>837</v>
-      </c>
-      <c r="D412" t="s">
+      <c r="A412" s="4">
+        <v>395</v>
+      </c>
+      <c r="B412" s="4" t="s">
         <v>838</v>
       </c>
-      <c r="E412">
-        <v>393</v>
+      <c r="C412" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D412" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="E412" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F412" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G412" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H412" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I412" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J412" s="4">
+        <v>0</v>
+      </c>
+      <c r="K412" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L412" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="4">
+        <v>396</v>
+      </c>
+      <c r="B413" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="C413" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D413" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="E413" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F413" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G413" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H413" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I413" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J413" s="4">
+        <v>0</v>
+      </c>
+      <c r="K413" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L413" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="4">
+        <v>397</v>
+      </c>
+      <c r="B414" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="C414" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D414" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="E414" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F414" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G414" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H414" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I414" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J414" s="4">
+        <v>0</v>
+      </c>
+      <c r="K414" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L414" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="3">
+        <v>398</v>
+      </c>
+      <c r="B415" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="C415" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="D415" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="E415" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F415" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G415" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H415" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I415" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J415" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K415" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L415" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="4">
+        <v>399</v>
+      </c>
+      <c r="B416" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="C416" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D416" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="E416" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F416" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G416" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H416" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I416" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J416" s="4">
+        <v>0</v>
+      </c>
+      <c r="K416" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L416" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="4">
+        <v>400</v>
+      </c>
+      <c r="B417" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="C417" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D417" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="E417" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F417" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G417" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H417" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I417" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J417" s="4">
+        <v>0</v>
+      </c>
+      <c r="K417" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L417" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="4">
+        <v>401</v>
+      </c>
+      <c r="B418" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="C418" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D418" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="E418" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F418" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G418" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H418" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I418" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J418" s="4">
+        <v>0</v>
+      </c>
+      <c r="K418" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L418" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="4">
+        <v>402</v>
+      </c>
+      <c r="B419" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="C419" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D419" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="E419" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F419" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G419" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H419" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I419" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J419" s="4">
+        <v>0</v>
+      </c>
+      <c r="K419" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L419" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="4">
+        <v>403</v>
+      </c>
+      <c r="B420" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="C420" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D420" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="E420" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F420" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G420" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H420" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I420" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J420" s="4">
+        <v>0</v>
+      </c>
+      <c r="K420" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L420" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="4">
+        <v>404</v>
+      </c>
+      <c r="B421" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="C421" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D421" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="E421" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F421" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G421" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H421" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I421" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J421" s="4">
+        <v>0</v>
+      </c>
+      <c r="K421" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L421" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="4">
+        <v>405</v>
+      </c>
+      <c r="B422" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="C422" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D422" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="E422" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F422" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G422" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H422" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I422" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J422" s="4">
+        <v>0</v>
+      </c>
+      <c r="K422" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L422" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="4">
+        <v>406</v>
+      </c>
+      <c r="B423" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="C423" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D423" s="4" t="s">
+        <v>861</v>
+      </c>
+      <c r="E423" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F423" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G423" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H423" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I423" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J423" s="4">
+        <v>0</v>
+      </c>
+      <c r="K423" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L423" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="4">
+        <v>407</v>
+      </c>
+      <c r="B424" s="4" t="s">
+        <v>862</v>
+      </c>
+      <c r="C424" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D424" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="E424" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F424" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G424" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H424" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I424" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J424" s="4">
+        <v>0</v>
+      </c>
+      <c r="K424" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L424" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="4">
+        <v>408</v>
+      </c>
+      <c r="B425" s="4" t="s">
+        <v>864</v>
+      </c>
+      <c r="C425" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D425" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="E425" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F425" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G425" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H425" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I425" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J425" s="4">
+        <v>0</v>
+      </c>
+      <c r="K425" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L425" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="4">
+        <v>409</v>
+      </c>
+      <c r="B426" s="4" t="s">
+        <v>866</v>
+      </c>
+      <c r="C426" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D426" s="4" t="s">
+        <v>867</v>
+      </c>
+      <c r="E426" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F426" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G426" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H426" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I426" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J426" s="4">
+        <v>0</v>
+      </c>
+      <c r="K426" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L426" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="4">
+        <v>410</v>
+      </c>
+      <c r="B427" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="C427" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D427" s="4" t="s">
+        <v>869</v>
+      </c>
+      <c r="E427" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F427" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G427" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H427" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I427" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J427" s="4">
+        <v>0</v>
+      </c>
+      <c r="K427" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L427" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="4">
+        <v>411</v>
+      </c>
+      <c r="B428" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="C428" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D428" s="4" t="s">
+        <v>871</v>
+      </c>
+      <c r="E428" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F428" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G428" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H428" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I428" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J428" s="4">
+        <v>0</v>
+      </c>
+      <c r="K428" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L428" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="4">
+        <v>412</v>
+      </c>
+      <c r="B429" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="C429" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D429" s="4" t="s">
+        <v>873</v>
+      </c>
+      <c r="E429" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F429" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G429" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H429" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I429" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J429" s="4">
+        <v>0</v>
+      </c>
+      <c r="K429" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L429" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="4">
+        <v>413</v>
+      </c>
+      <c r="B430" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="C430" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D430" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="E430" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F430" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G430" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H430" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I430" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J430" s="4">
+        <v>0</v>
+      </c>
+      <c r="K430" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L430" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="4">
+        <v>414</v>
+      </c>
+      <c r="B431" s="4" t="s">
+        <v>876</v>
+      </c>
+      <c r="C431" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D431" s="4" t="s">
+        <v>877</v>
+      </c>
+      <c r="E431" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F431" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G431" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H431" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I431" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J431" s="4">
+        <v>0</v>
+      </c>
+      <c r="K431" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L431" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="4">
+        <v>415</v>
+      </c>
+      <c r="B432" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="C432" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D432" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="E432" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F432" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G432" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H432" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I432" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J432" s="4">
+        <v>0</v>
+      </c>
+      <c r="K432" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L432" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="4">
+        <v>416</v>
+      </c>
+      <c r="B433" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="C433" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D433" s="4" t="s">
+        <v>881</v>
+      </c>
+      <c r="E433" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F433" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G433" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H433" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I433" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J433" s="4">
+        <v>0</v>
+      </c>
+      <c r="K433" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L433" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="4">
+        <v>417</v>
+      </c>
+      <c r="B434" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="C434" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D434" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="E434" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F434" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G434" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H434" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I434" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J434" s="4">
+        <v>0</v>
+      </c>
+      <c r="K434" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L434" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="4">
+        <v>418</v>
+      </c>
+      <c r="B435" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="C435" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D435" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="E435" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F435" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G435" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H435" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I435" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J435" s="4">
+        <v>0</v>
+      </c>
+      <c r="K435" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L435" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="4">
+        <v>419</v>
+      </c>
+      <c r="B436" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="C436" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D436" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="E436" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F436" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G436" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H436" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I436" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J436" s="4">
+        <v>0</v>
+      </c>
+      <c r="K436" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L436" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="4">
+        <v>420</v>
+      </c>
+      <c r="B437" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="C437" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D437" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="E437" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F437" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G437" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H437" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I437" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J437" s="4">
+        <v>0</v>
+      </c>
+      <c r="K437" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L437" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="4">
+        <v>421</v>
+      </c>
+      <c r="B438" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="C438" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D438" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="E438" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F438" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G438" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H438" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I438" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J438" s="4">
+        <v>0</v>
+      </c>
+      <c r="K438" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L438" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="4">
+        <v>422</v>
+      </c>
+      <c r="B439" s="4" t="s">
+        <v>892</v>
+      </c>
+      <c r="C439" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D439" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="E439" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F439" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G439" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H439" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I439" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J439" s="4">
+        <v>0</v>
+      </c>
+      <c r="K439" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L439" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="4">
+        <v>423</v>
+      </c>
+      <c r="B440" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="C440" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D440" s="4" t="s">
+        <v>895</v>
+      </c>
+      <c r="E440" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F440" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G440" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H440" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I440" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J440" s="4">
+        <v>0</v>
+      </c>
+      <c r="K440" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L440" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="4">
+        <v>424</v>
+      </c>
+      <c r="B441" s="4" t="s">
+        <v>896</v>
+      </c>
+      <c r="C441" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D441" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="E441" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F441" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G441" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H441" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I441" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J441" s="4">
+        <v>0</v>
+      </c>
+      <c r="K441" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L441" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="4">
+        <v>425</v>
+      </c>
+      <c r="B442" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="C442" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D442" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="E442" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F442" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G442" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H442" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I442" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J442" s="4">
+        <v>0</v>
+      </c>
+      <c r="K442" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L442" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="4">
+        <v>426</v>
+      </c>
+      <c r="B443" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="C443" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D443" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="E443" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F443" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G443" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H443" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I443" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J443" s="4">
+        <v>0</v>
+      </c>
+      <c r="K443" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L443" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="4">
+        <v>427</v>
+      </c>
+      <c r="B444" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="C444" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D444" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="E444" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F444" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G444" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H444" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I444" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J444" s="4">
+        <v>0</v>
+      </c>
+      <c r="K444" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L444" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="3">
+        <v>428</v>
+      </c>
+      <c r="B445" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="C445" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="D445" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="E445" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F445" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G445" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H445" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I445" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J445" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K445" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L445" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="3">
+        <v>429</v>
+      </c>
+      <c r="B446" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="C446" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="D446" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="E446" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F446" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G446" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H446" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I446" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J446" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K446" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L446" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="3">
+        <v>430</v>
+      </c>
+      <c r="B447" s="3" t="s">
+        <v>908</v>
+      </c>
+      <c r="C447" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="D447" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="E447" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F447" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G447" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H447" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I447" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J447" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K447" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L447" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="3">
+        <v>431</v>
+      </c>
+      <c r="B448" s="3" t="s">
+        <v>910</v>
+      </c>
+      <c r="C448" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="D448" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="E448" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F448" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G448" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H448" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I448" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J448" s="3">
+        <v>9223372036</v>
+      </c>
+      <c r="K448" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L448" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="4">
+        <v>432</v>
+      </c>
+      <c r="B449" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="C449" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D449" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="E449" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F449" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G449" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H449" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I449" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J449" s="4">
+        <v>0</v>
+      </c>
+      <c r="K449" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L449" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="s">
+        <v>914</v>
+      </c>
+      <c r="B451" t="s">
+        <v>915</v>
+      </c>
+      <c r="D451" t="s">
+        <v>916</v>
+      </c>
+      <c r="E451">
+        <v>432</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-05.xlsx
+++ b/report-2026-06-05.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="939">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-05T19:28:52+05:30</t>
+    <t>Generated 2026-06-05T19:59:20+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-05T19:26:51+05:30 (2m0s ago)</t>
+    <t>2026-06-05T19:57:20+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -2755,16 +2755,82 @@
     <t>04:15:03.846</t>
   </si>
   <si>
-    <t>2026-06-05T19:26:51.9335198+05:30</t>
-  </si>
-  <si>
-    <t>19:26:51.933</t>
+    <t>2026-06-05T19:29:23.456703+05:30</t>
+  </si>
+  <si>
+    <t>19:29:23.456</t>
+  </si>
+  <si>
+    <t>2026-06-05T19:31:53.7202197+05:30</t>
+  </si>
+  <si>
+    <t>19:31:53.720</t>
+  </si>
+  <si>
+    <t>2026-06-05T19:34:23.6338923+05:30</t>
+  </si>
+  <si>
+    <t>19:34:23.633</t>
+  </si>
+  <si>
+    <t>2026-06-05T19:36:53.6913101+05:30</t>
+  </si>
+  <si>
+    <t>19:36:53.691</t>
+  </si>
+  <si>
+    <t>2026-06-05T19:39:23.7429587+05:30</t>
+  </si>
+  <si>
+    <t>19:39:23.742</t>
+  </si>
+  <si>
+    <t>2026-06-05T19:41:53.8388132+05:30</t>
+  </si>
+  <si>
+    <t>19:41:53.838</t>
+  </si>
+  <si>
+    <t>2026-06-05T19:44:23.7583805+05:30</t>
+  </si>
+  <si>
+    <t>19:44:23.758</t>
+  </si>
+  <si>
+    <t>2026-06-05T19:46:53.8500478+05:30</t>
+  </si>
+  <si>
+    <t>19:46:53.850</t>
+  </si>
+  <si>
+    <t>2026-06-05T19:49:23.5455116+05:30</t>
+  </si>
+  <si>
+    <t>19:49:23.545</t>
+  </si>
+  <si>
+    <t>2026-06-05T19:51:53.6179428+05:30</t>
+  </si>
+  <si>
+    <t>19:51:53.617</t>
+  </si>
+  <si>
+    <t>2026-06-05T19:54:23.6683135+05:30</t>
+  </si>
+  <si>
+    <t>19:54:23.668</t>
+  </si>
+  <si>
+    <t>2026-06-05T19:56:54.0317774+05:30</t>
+  </si>
+  <si>
+    <t>19:56:54.031</t>
   </si>
   <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-05T19:28:52+05:30</t>
+    <t>2026-06-05T19:59:20+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -3319,7 +3385,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.37</t>
+          <t>10.0.55</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -3359,12 +3425,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 13s</t>
+          <t>0h 2m 15s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-05 19:26:38</t>
+          <t>2026-06-05 19:57:05</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3374,12 +3440,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-05 19:26:38</t>
+          <t>2026-06-05 19:57:05</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0h 1m 10s</t>
+          <t>never</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -3389,7 +3455,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:28:52</t>
+          <t>19:59:20</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3492,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.37</t>
+          <t>10.0.55</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -3441,22 +3507,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stale</t>
+          <t>good</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>119022.5</t>
+          <t>116999.3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>944</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -3466,7 +3532,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -3481,7 +3547,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-05 19:26:38</t>
+          <t>2026-06-05 19:57:05</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3496,7 +3562,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:28:52</t>
+          <t>19:59:20</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3681,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-05T19:26:51.9335198+05:30</t>
+          <t>2026-06-05T19:56:54.0317774+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3625,7 +3691,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19:26:51.933</t>
+          <t>19:56:54.031</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -8442,6 +8508,1056 @@
         </is>
       </c>
       <c r="G135" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>1780669672856</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>19:57:52</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>MjsFG9V8</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>1780669672952</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>19:57:52</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>MjsFG9V8</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>1780669674287</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>19:57:54</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>N0AAY8jq</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>1780669674493</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>19:57:54</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>N0AAY8jq</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>1780669675366</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>19:57:55</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>4AeL4YHi</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>1780669675576</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>19:57:55</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>4AeL4YHi</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>1780669676013</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>19:57:56</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>1X7dFtO8</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>1780669676226</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>19:57:56</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>1X7dFtO8</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>1780669676564</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>19:57:56</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>6K3kn8Za</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>1780669676783</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>19:57:56</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>6K3kn8Za</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>1780669677463</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>19:57:57</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>cSsvb8uH</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>1780669677658</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>19:57:57</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>cSsvb8uH</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>1780669677998</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>19:57:57</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>uZ1pelq0</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>1780669678215</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>19:57:58</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>uZ1pelq0</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>1780669678296</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>19:57:58</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>VywAxCqk</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>1780669678496</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>19:57:58</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>VywAxCqk</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>1780669678621</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>19:57:58</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>81U2EbSQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>1780669678739</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>19:57:58</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>81U2EbSQ</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>1780669679016</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>19:57:59</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>7gDz2bAn</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>1780669679096</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>19:57:59</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>7gDz2bAn</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>1780669679234</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>19:57:59</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>aF0dbbMV</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>1780669679300</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>19:57:59</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>aF0dbbMV</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>1780669725027</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>19:58:45</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>37BbT8Ao</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>1780669725086</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>19:58:45</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>37BbT8Ao</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>1780669726335</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>19:58:46</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>s1IIoiWh</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>1780669726400</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>19:58:46</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>s1IIoiWh</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>1780669727307</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>19:58:47</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>7BU6abnZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>1780669727373</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>19:58:47</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>7BU6abnZ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>1780669727998</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>19:58:47</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>GBIkJMi3</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>1780669728055</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>19:58:48</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>GBIkJMi3</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -25047,18 +26163,436 @@
         <v>43</v>
       </c>
     </row>
+    <row r="450">
+      <c r="A450" s="4">
+        <v>433</v>
+      </c>
+      <c r="B450" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="C450" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D450" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="E450" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F450" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G450" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H450" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I450" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J450" s="4">
+        <v>0</v>
+      </c>
+      <c r="K450" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L450" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="451">
-      <c r="A451" t="s">
-        <v>914</v>
-      </c>
-      <c r="B451" t="s">
-        <v>915</v>
-      </c>
-      <c r="D451" t="s">
+      <c r="A451" s="4">
+        <v>434</v>
+      </c>
+      <c r="B451" s="4" t="s">
         <v>916</v>
       </c>
-      <c r="E451">
-        <v>432</v>
+      <c r="C451" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D451" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="E451" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F451" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G451" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H451" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I451" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J451" s="4">
+        <v>0</v>
+      </c>
+      <c r="K451" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L451" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="4">
+        <v>435</v>
+      </c>
+      <c r="B452" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="C452" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D452" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="E452" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F452" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G452" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H452" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I452" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J452" s="4">
+        <v>0</v>
+      </c>
+      <c r="K452" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L452" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="4">
+        <v>436</v>
+      </c>
+      <c r="B453" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="C453" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D453" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="E453" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F453" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G453" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H453" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I453" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J453" s="4">
+        <v>0</v>
+      </c>
+      <c r="K453" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L453" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="4">
+        <v>437</v>
+      </c>
+      <c r="B454" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="C454" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D454" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="E454" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F454" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G454" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H454" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I454" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J454" s="4">
+        <v>0</v>
+      </c>
+      <c r="K454" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L454" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="4">
+        <v>438</v>
+      </c>
+      <c r="B455" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="C455" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D455" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="E455" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F455" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G455" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H455" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I455" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J455" s="4">
+        <v>0</v>
+      </c>
+      <c r="K455" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L455" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="4">
+        <v>439</v>
+      </c>
+      <c r="B456" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="C456" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D456" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="E456" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F456" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G456" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H456" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I456" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J456" s="4">
+        <v>0</v>
+      </c>
+      <c r="K456" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L456" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="4">
+        <v>440</v>
+      </c>
+      <c r="B457" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="C457" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D457" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="E457" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F457" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G457" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H457" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I457" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J457" s="4">
+        <v>0</v>
+      </c>
+      <c r="K457" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L457" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="4">
+        <v>441</v>
+      </c>
+      <c r="B458" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="C458" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D458" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="E458" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F458" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G458" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H458" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I458" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J458" s="4">
+        <v>0</v>
+      </c>
+      <c r="K458" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L458" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="4">
+        <v>442</v>
+      </c>
+      <c r="B459" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="C459" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D459" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="E459" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F459" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G459" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H459" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I459" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J459" s="4">
+        <v>0</v>
+      </c>
+      <c r="K459" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L459" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="4">
+        <v>443</v>
+      </c>
+      <c r="B460" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="C460" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D460" s="4" t="s">
+        <v>935</v>
+      </c>
+      <c r="E460" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F460" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G460" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H460" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I460" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J460" s="4">
+        <v>0</v>
+      </c>
+      <c r="K460" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L460" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="s">
+        <v>936</v>
+      </c>
+      <c r="B462" t="s">
+        <v>937</v>
+      </c>
+      <c r="D462" t="s">
+        <v>938</v>
+      </c>
+      <c r="E462">
+        <v>443</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-05.xlsx
+++ b/report-2026-06-05.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="941">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-05T19:59:20+05:30</t>
+    <t>Generated 2026-06-05T20:10:08+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-05T19:57:20+05:30 (2m0s ago)</t>
+    <t>2026-06-05T20:08:07+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -2827,10 +2827,16 @@
     <t>19:56:54.031</t>
   </si>
   <si>
+    <t>2026-06-05T20:07:30.9400298+05:30</t>
+  </si>
+  <si>
+    <t>20:07:30.940</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-05T19:59:20+05:30</t>
+    <t>2026-06-05T20:10:08+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -3425,12 +3431,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 15s</t>
+          <t>0h 2m 16s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-05 19:57:05</t>
+          <t>2026-06-05 20:07:51</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3440,12 +3446,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-05 19:57:05</t>
+          <t>2026-06-05 20:07:51</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>0h 0m 42s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -3455,7 +3461,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:59:20</t>
+          <t>20:10:08</t>
         </is>
       </c>
     </row>
@@ -3512,17 +3518,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>116999.3</t>
+          <t>155243.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -3532,7 +3538,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -3547,12 +3553,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-05 19:57:05</t>
+          <t>2026-06-05 20:07:51</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>0h 0m 22s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -3562,7 +3568,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:59:20</t>
+          <t>20:10:08</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3687,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-05T19:56:54.0317774+05:30</t>
+          <t>2026-06-05T20:07:30.9400298+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3691,7 +3697,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19:56:54.031</t>
+          <t>20:07:30.940</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -9558,6 +9564,706 @@
         </is>
       </c>
       <c r="G165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>1780670368837</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>20:09:28</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>bIsJ3eqy</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>1780670369042</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>20:09:29</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>bIsJ3eqy</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>1780670369267</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>20:09:29</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>xJaMZzcI</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>1780670369456</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>20:09:29</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>xJaMZzcI</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>1780670369473</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>20:09:29</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>p2IFZeNO</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>1780670369678</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>20:09:29</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>bivC58AV</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>1780670369710</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>20:09:29</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>p2IFZeNO</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>1780670369854</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>20:09:29</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>ksjGHZsW</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>1780670369890</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>20:09:29</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>bivC58AV</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>1780670370036</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>20:09:30</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>ksjGHZsW</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>1780670370067</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>20:09:30</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>ZIFUXhIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>1780670370299</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>20:09:30</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>ZIFUXhIO</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>1780670370302</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>20:09:30</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>3MUmbykV</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>1780670370479</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>20:09:30</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>3MUmbykV</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>1780670370706</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>20:09:30</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>6mTVgs9u</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>1780670370886</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>20:09:30</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>fKNm1eWn</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>1780670370912</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>20:09:30</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>6mTVgs9u</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>1780670371129</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>20:09:31</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>V4XyBsrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>1780670372103</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>20:09:32</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>fKNm1eWn</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>1780670372275</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>20:09:32</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>V4XyBsrp</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -26581,18 +27287,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="462">
-      <c r="A462" t="s">
+    <row r="461">
+      <c r="A461" s="4">
+        <v>444</v>
+      </c>
+      <c r="B461" s="4" t="s">
         <v>936</v>
       </c>
-      <c r="B462" t="s">
+      <c r="C461" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D461" s="4" t="s">
         <v>937</v>
       </c>
-      <c r="D462" t="s">
+      <c r="E461" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F461" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G461" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H461" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I461" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J461" s="4">
+        <v>0</v>
+      </c>
+      <c r="K461" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L461" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="s">
         <v>938</v>
       </c>
-      <c r="E462">
-        <v>443</v>
+      <c r="B463" t="s">
+        <v>939</v>
+      </c>
+      <c r="D463" t="s">
+        <v>940</v>
+      </c>
+      <c r="E463">
+        <v>444</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-05.xlsx
+++ b/report-2026-06-05.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="941">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="951">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-05T20:10:08+05:30</t>
+    <t>Generated 2026-06-05T20:21:26+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-05T20:08:07+05:30 (2m0s ago)</t>
+    <t>2026-06-05T20:19:26+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -2833,10 +2833,40 @@
     <t>20:07:30.940</t>
   </si>
   <si>
+    <t>2026-06-05T20:10:39.5083003+05:30</t>
+  </si>
+  <si>
+    <t>20:10:39.508</t>
+  </si>
+  <si>
+    <t>2026-06-05T20:13:09.6075751+05:30</t>
+  </si>
+  <si>
+    <t>20:13:09.607</t>
+  </si>
+  <si>
+    <t>2026-06-05T20:15:39.6159395+05:30</t>
+  </si>
+  <si>
+    <t>20:15:39.615</t>
+  </si>
+  <si>
+    <t>2026-06-05T20:17:31.1731071+05:30</t>
+  </si>
+  <si>
+    <t>20:17:31.173</t>
+  </si>
+  <si>
+    <t>2026-06-05T20:19:26.1993489+05:30</t>
+  </si>
+  <si>
+    <t>20:19:26.199</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-05T20:10:08+05:30</t>
+    <t>2026-06-05T20:21:26+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -3436,7 +3466,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-05 20:07:51</t>
+          <t>2026-06-05 20:19:09</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3446,12 +3476,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-05 20:07:51</t>
+          <t>2026-06-05 20:19:09</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0h 0m 42s</t>
+          <t>never</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -3461,7 +3491,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20:10:08</t>
+          <t>20:21:26</t>
         </is>
       </c>
     </row>
@@ -3518,17 +3548,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>155243.5</t>
+          <t>103039.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -3553,12 +3583,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-05 20:07:51</t>
+          <t>2026-06-05 20:19:09</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0h 0m 22s</t>
+          <t>never</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -3568,7 +3598,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20:10:08</t>
+          <t>20:21:26</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3717,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-05T20:07:30.9400298+05:30</t>
+          <t>2026-06-05T20:19:26.1993489+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3697,7 +3727,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20:07:30.940</t>
+          <t>20:19:26.199</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -10264,6 +10294,2036 @@
         </is>
       </c>
       <c r="G185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>1780670443573</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>20:10:43</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>1c6YYG09</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>1780670443821</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>20:10:43</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>1c6YYG09</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>1780670444526</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>20:10:44</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>jxYX1Cv0</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>1780670444723</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>20:10:44</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>jxYX1Cv0</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>1780670445242</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>20:10:45</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>1nR09LmZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>1780670445446</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>20:10:45</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>1nR09LmZ</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>1780670445895</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>20:10:45</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>MP3OKD2V</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>1780670446123</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>20:10:46</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>MP3OKD2V</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>1780670446471</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>20:10:46</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>USfS6ZDL</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>1780670446700</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>20:10:46</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>USfS6ZDL</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>1780670447080</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>20:10:47</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>A24KOTff</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>1780670447278</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>20:10:47</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>A24KOTff</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>1780670447645</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>20:10:47</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>W8e6BwT2</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>1780670447852</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>20:10:47</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>W8e6BwT2</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>1780670447969</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>20:10:47</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>fuY7AtFa</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201">
+        <v>1780670448178</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>20:10:48</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>g53XH5eF</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <v>1780670448196</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>20:10:48</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>fuY7AtFa</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203">
+        <v>1780670448365</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>20:10:48</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>MPzkKjh9</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204">
+        <v>1780670448372</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>20:10:48</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>g53XH5eF</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205">
+        <v>1780670448576</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>20:10:48</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>MPzkKjh9</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206">
+        <v>1780670448588</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>20:10:48</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>ogmxsnYh</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207">
+        <v>1780670448792</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>20:10:48</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>ogmxsnYh</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208">
+        <v>1780670449425</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>20:10:49</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>rduJDbNM</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <v>1780670449624</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>20:10:49</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>rduJDbNM</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210">
+        <v>1780670450168</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>20:10:50</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>LLgZIRCK</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <v>1780670450297</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>20:10:50</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>YTO19LpE</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212">
+        <v>1780670450418</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>20:10:50</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>LLgZIRCK</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213">
+        <v>1780670450522</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>20:10:50</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>IcB8pDtP</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214">
+        <v>1780670450554</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>20:10:50</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>YTO19LpE</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <v>1780670450737</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>20:10:50</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>IcB8pDtP</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>1780670973723</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>20:19:33</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>NNSdhdbm</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>1780670973747</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>20:19:33</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>NNSdhdbm</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>1780670973897</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>20:19:33</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>5l3r5gAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>1780670973905</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>20:19:33</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>5l3r5gAO</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>1780670974054</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>20:19:34</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>93mfSwL3</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>1780670974064</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>20:19:34</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>93mfSwL3</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>1780670974231</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>20:19:34</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>IlexVnZo</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>1780670974243</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>20:19:34</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>IlexVnZo</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>1780670974392</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>20:19:34</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>iBruIc7M</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>1780670974401</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>20:19:34</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>iBruIc7M</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>1780670974585</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>20:19:34</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>PFQVPubQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>1780670974602</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>20:19:34</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>PFQVPubQ</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>1780670974743</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>20:19:34</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>69ifijHv</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <v>1780670974777</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>20:19:34</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>69ifijHv</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <v>1780670974890</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>20:19:34</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>ceiJV6Pj</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <v>1780670974906</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>20:19:34</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>ceiJV6Pj</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <v>1780670975051</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>20:19:35</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>kOfHvlgb</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>1780670975065</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>20:19:35</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>kOfHvlgb</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <v>1780670975270</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>20:19:35</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>vqNXQUDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <v>1780670975288</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>20:19:35</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>vqNXQUDF</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <v>1780670993399</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>20:19:53</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>TFyjD9Im</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>1780670993415</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>20:19:53</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>TFyjD9Im</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>1780671025054</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>20:20:25</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>w1bxkONx</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>1780671025274</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>20:20:25</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>w1bxkONx</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>1780671026180</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>20:20:26</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>9Vdgqql3</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>1780671026384</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>20:20:26</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>9Vdgqql3</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>1780671027036</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>20:20:27</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>t30JSB7Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>1780671027234</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>20:20:27</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>t30JSB7Y</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -27325,18 +29385,208 @@
         <v>43</v>
       </c>
     </row>
+    <row r="462">
+      <c r="A462" s="4">
+        <v>445</v>
+      </c>
+      <c r="B462" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="C462" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D462" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="E462" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F462" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G462" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H462" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I462" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J462" s="4">
+        <v>0</v>
+      </c>
+      <c r="K462" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L462" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="463">
-      <c r="A463" t="s">
-        <v>938</v>
-      </c>
-      <c r="B463" t="s">
-        <v>939</v>
-      </c>
-      <c r="D463" t="s">
+      <c r="A463" s="4">
+        <v>446</v>
+      </c>
+      <c r="B463" s="4" t="s">
         <v>940</v>
       </c>
-      <c r="E463">
-        <v>444</v>
+      <c r="C463" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D463" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="E463" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F463" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G463" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H463" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I463" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J463" s="4">
+        <v>0</v>
+      </c>
+      <c r="K463" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L463" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="4">
+        <v>447</v>
+      </c>
+      <c r="B464" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="C464" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D464" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="E464" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F464" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G464" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H464" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I464" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J464" s="4">
+        <v>0</v>
+      </c>
+      <c r="K464" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L464" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="4">
+        <v>448</v>
+      </c>
+      <c r="B465" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="C465" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D465" s="4" t="s">
+        <v>945</v>
+      </c>
+      <c r="E465" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F465" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G465" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H465" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I465" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J465" s="4">
+        <v>0</v>
+      </c>
+      <c r="K465" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L465" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="4">
+        <v>449</v>
+      </c>
+      <c r="B466" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="C466" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D466" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="E466" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F466" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G466" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H466" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I466" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J466" s="4">
+        <v>0</v>
+      </c>
+      <c r="K466" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L466" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="s">
+        <v>948</v>
+      </c>
+      <c r="B468" t="s">
+        <v>949</v>
+      </c>
+      <c r="D468" t="s">
+        <v>950</v>
+      </c>
+      <c r="E468">
+        <v>449</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-05.xlsx
+++ b/report-2026-06-05.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="951">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="965">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-05T20:21:26+05:30</t>
+    <t>Generated 2026-06-05T20:38:50+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-05T20:19:26+05:30 (2m0s ago)</t>
+    <t>2026-06-05T20:36:49+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -2863,10 +2863,52 @@
     <t>20:19:26.199</t>
   </si>
   <si>
+    <t>2026-06-05T20:21:57.7263768+05:30</t>
+  </si>
+  <si>
+    <t>20:21:57.726</t>
+  </si>
+  <si>
+    <t>2026-06-05T20:24:27.6931738+05:30</t>
+  </si>
+  <si>
+    <t>20:24:27.693</t>
+  </si>
+  <si>
+    <t>2026-06-05T20:26:57.8226787+05:30</t>
+  </si>
+  <si>
+    <t>20:26:57.822</t>
+  </si>
+  <si>
+    <t>2026-06-05T20:29:27.8486279+05:30</t>
+  </si>
+  <si>
+    <t>20:29:27.848</t>
+  </si>
+  <si>
+    <t>2026-06-05T20:31:57.8697518+05:30</t>
+  </si>
+  <si>
+    <t>20:31:57.869</t>
+  </si>
+  <si>
+    <t>2026-06-05T20:34:27.8120083+05:30</t>
+  </si>
+  <si>
+    <t>20:34:27.812</t>
+  </si>
+  <si>
+    <t>2026-06-05T20:36:49.9080264+05:30</t>
+  </si>
+  <si>
+    <t>20:36:49.908</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-05T20:21:26+05:30</t>
+    <t>2026-06-05T20:38:50+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -3466,7 +3508,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-05 20:19:09</t>
+          <t>2026-06-05 20:36:34</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3476,12 +3518,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-05 20:19:09</t>
+          <t>2026-06-05 20:36:34</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>0h 5m 37s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -3491,7 +3533,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20:21:26</t>
+          <t>20:38:50</t>
         </is>
       </c>
     </row>
@@ -3548,17 +3590,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>351.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>103039.5</t>
+          <t>486119.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>405</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -3568,7 +3610,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -3583,12 +3625,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-05 20:19:09</t>
+          <t>2026-06-05 20:36:34</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>0h 3m 37s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -3598,7 +3640,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20:21:26</t>
+          <t>20:38:50</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3759,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-05T20:19:26.1993489+05:30</t>
+          <t>2026-06-05T20:36:49.9080264+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3727,7 +3769,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20:19:26.199</t>
+          <t>20:36:49.908</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -29575,18 +29617,284 @@
         <v>43</v>
       </c>
     </row>
+    <row r="467">
+      <c r="A467" s="4">
+        <v>450</v>
+      </c>
+      <c r="B467" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="C467" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D467" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="E467" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F467" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G467" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H467" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I467" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J467" s="4">
+        <v>0</v>
+      </c>
+      <c r="K467" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L467" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="468">
-      <c r="A468" t="s">
-        <v>948</v>
-      </c>
-      <c r="B468" t="s">
-        <v>949</v>
-      </c>
-      <c r="D468" t="s">
+      <c r="A468" s="4">
+        <v>451</v>
+      </c>
+      <c r="B468" s="4" t="s">
         <v>950</v>
       </c>
-      <c r="E468">
-        <v>449</v>
+      <c r="C468" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D468" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="E468" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F468" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G468" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H468" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I468" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J468" s="4">
+        <v>0</v>
+      </c>
+      <c r="K468" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L468" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="4">
+        <v>452</v>
+      </c>
+      <c r="B469" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="C469" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D469" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="E469" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F469" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G469" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H469" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I469" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J469" s="4">
+        <v>0</v>
+      </c>
+      <c r="K469" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L469" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="4">
+        <v>453</v>
+      </c>
+      <c r="B470" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="C470" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D470" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="E470" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F470" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G470" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H470" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I470" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J470" s="4">
+        <v>0</v>
+      </c>
+      <c r="K470" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L470" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="4">
+        <v>454</v>
+      </c>
+      <c r="B471" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="C471" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D471" s="4" t="s">
+        <v>957</v>
+      </c>
+      <c r="E471" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F471" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G471" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H471" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I471" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J471" s="4">
+        <v>0</v>
+      </c>
+      <c r="K471" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L471" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="4">
+        <v>455</v>
+      </c>
+      <c r="B472" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="C472" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D472" s="4" t="s">
+        <v>959</v>
+      </c>
+      <c r="E472" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F472" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G472" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H472" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I472" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J472" s="4">
+        <v>0</v>
+      </c>
+      <c r="K472" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L472" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="4">
+        <v>456</v>
+      </c>
+      <c r="B473" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="C473" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D473" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="E473" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F473" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G473" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H473" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I473" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J473" s="4">
+        <v>0</v>
+      </c>
+      <c r="K473" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L473" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="s">
+        <v>962</v>
+      </c>
+      <c r="B475" t="s">
+        <v>963</v>
+      </c>
+      <c r="D475" t="s">
+        <v>964</v>
+      </c>
+      <c r="E475">
+        <v>456</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-05.xlsx
+++ b/report-2026-06-05.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="973">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-05T20:38:50+05:30</t>
+    <t>Generated 2026-06-05T20:49:44+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-05T20:36:49+05:30 (2m0s ago)</t>
+    <t>2026-06-05T20:47:44+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -2905,10 +2905,34 @@
     <t>20:36:49.908</t>
   </si>
   <si>
+    <t>2026-06-05T20:39:21.4747787+05:30</t>
+  </si>
+  <si>
+    <t>20:39:21.474</t>
+  </si>
+  <si>
+    <t>2026-06-05T20:41:51.4686681+05:30</t>
+  </si>
+  <si>
+    <t>20:41:51.468</t>
+  </si>
+  <si>
+    <t>2026-06-05T20:44:21.5914489+05:30</t>
+  </si>
+  <si>
+    <t>20:44:21.591</t>
+  </si>
+  <si>
+    <t>2026-06-05T20:46:51.5453333+05:30</t>
+  </si>
+  <si>
+    <t>20:46:51.545</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-05T20:38:50+05:30</t>
+    <t>2026-06-05T20:49:44+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -3503,12 +3527,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 16s</t>
+          <t>0h 2m 14s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-05 20:36:34</t>
+          <t>2026-06-05 20:47:30</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3518,12 +3542,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-05 20:36:34</t>
+          <t>2026-06-05 20:47:30</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0h 5m 37s</t>
+          <t>0h 0m 5s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -3533,7 +3557,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20:38:50</t>
+          <t>20:49:44</t>
         </is>
       </c>
     </row>
@@ -3590,17 +3614,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>351.0</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>486119.5</t>
+          <t>258250.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -3610,7 +3634,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -3625,12 +3649,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-05 20:36:34</t>
+          <t>2026-06-05 20:47:30</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0h 3m 37s</t>
+          <t>0h 0m 0s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -3640,7 +3664,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20:38:50</t>
+          <t>20:49:44</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3783,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-05T20:36:49.9080264+05:30</t>
+          <t>2026-06-05T20:46:51.5453333+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3769,7 +3793,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20:36:49.908</t>
+          <t>20:46:51.545</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -29883,18 +29907,170 @@
         <v>43</v>
       </c>
     </row>
+    <row r="474">
+      <c r="A474" s="4">
+        <v>457</v>
+      </c>
+      <c r="B474" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="C474" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D474" s="4" t="s">
+        <v>963</v>
+      </c>
+      <c r="E474" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F474" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G474" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H474" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I474" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J474" s="4">
+        <v>0</v>
+      </c>
+      <c r="K474" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L474" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="475">
-      <c r="A475" t="s">
-        <v>962</v>
-      </c>
-      <c r="B475" t="s">
-        <v>963</v>
-      </c>
-      <c r="D475" t="s">
+      <c r="A475" s="4">
+        <v>458</v>
+      </c>
+      <c r="B475" s="4" t="s">
         <v>964</v>
       </c>
-      <c r="E475">
-        <v>456</v>
+      <c r="C475" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D475" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="E475" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F475" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G475" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H475" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I475" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J475" s="4">
+        <v>0</v>
+      </c>
+      <c r="K475" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L475" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="4">
+        <v>459</v>
+      </c>
+      <c r="B476" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="C476" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D476" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="E476" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F476" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G476" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H476" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I476" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J476" s="4">
+        <v>0</v>
+      </c>
+      <c r="K476" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L476" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="4">
+        <v>460</v>
+      </c>
+      <c r="B477" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="C477" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D477" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="E477" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F477" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G477" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H477" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I477" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J477" s="4">
+        <v>0</v>
+      </c>
+      <c r="K477" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L477" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="s">
+        <v>970</v>
+      </c>
+      <c r="B479" t="s">
+        <v>971</v>
+      </c>
+      <c r="D479" t="s">
+        <v>972</v>
+      </c>
+      <c r="E479">
+        <v>460</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-05.xlsx
+++ b/report-2026-06-05.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="973">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="981">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-05T20:49:44+05:30</t>
+    <t>Generated 2026-06-05T20:59:43+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-05T20:47:44+05:30 (2m0s ago)</t>
+    <t>2026-06-05T20:57:43+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -2929,10 +2929,34 @@
     <t>20:46:51.545</t>
   </si>
   <si>
+    <t>2026-06-05T20:50:15.7605926+05:30</t>
+  </si>
+  <si>
+    <t>20:50:15.760</t>
+  </si>
+  <si>
+    <t>2026-06-05T20:52:45.9924451+05:30</t>
+  </si>
+  <si>
+    <t>20:52:45.992</t>
+  </si>
+  <si>
+    <t>2026-06-05T20:55:32.2747766+05:30</t>
+  </si>
+  <si>
+    <t>20:55:32.274</t>
+  </si>
+  <si>
+    <t>2026-06-05T20:57:43.611099+05:30</t>
+  </si>
+  <si>
+    <t>20:57:43.611</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-05T20:49:44+05:30</t>
+    <t>2026-06-05T20:59:43+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -3527,12 +3551,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 14s</t>
+          <t>0h 2m 15s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-05 20:47:30</t>
+          <t>2026-06-05 20:57:28</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3542,7 +3566,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-05 20:47:30</t>
+          <t>2026-06-05 20:57:28</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3557,7 +3581,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20:49:44</t>
+          <t>20:59:43</t>
         </is>
       </c>
     </row>
@@ -3614,17 +3638,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>258250.5</t>
+          <t>189224.7</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>983</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -3634,7 +3658,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -3649,7 +3673,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-05 20:47:30</t>
+          <t>2026-06-05 20:57:28</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3664,7 +3688,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20:49:44</t>
+          <t>20:59:43</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3807,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-05T20:46:51.5453333+05:30</t>
+          <t>2026-06-05T20:57:43.611099+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3793,7 +3817,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20:46:51.545</t>
+          <t>20:57:43.611</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -30059,18 +30083,170 @@
         <v>43</v>
       </c>
     </row>
+    <row r="478">
+      <c r="A478" s="4">
+        <v>461</v>
+      </c>
+      <c r="B478" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="C478" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D478" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="E478" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F478" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G478" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H478" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I478" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J478" s="4">
+        <v>0</v>
+      </c>
+      <c r="K478" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L478" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="479">
-      <c r="A479" t="s">
-        <v>970</v>
-      </c>
-      <c r="B479" t="s">
-        <v>971</v>
-      </c>
-      <c r="D479" t="s">
+      <c r="A479" s="4">
+        <v>462</v>
+      </c>
+      <c r="B479" s="4" t="s">
         <v>972</v>
       </c>
-      <c r="E479">
-        <v>460</v>
+      <c r="C479" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D479" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="E479" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F479" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G479" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H479" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I479" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J479" s="4">
+        <v>0</v>
+      </c>
+      <c r="K479" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L479" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="4">
+        <v>463</v>
+      </c>
+      <c r="B480" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="C480" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D480" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="E480" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F480" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G480" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H480" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I480" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J480" s="4">
+        <v>0</v>
+      </c>
+      <c r="K480" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L480" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="4">
+        <v>464</v>
+      </c>
+      <c r="B481" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="C481" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D481" s="4" t="s">
+        <v>977</v>
+      </c>
+      <c r="E481" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F481" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G481" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H481" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I481" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J481" s="4">
+        <v>0</v>
+      </c>
+      <c r="K481" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L481" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="s">
+        <v>978</v>
+      </c>
+      <c r="B483" t="s">
+        <v>979</v>
+      </c>
+      <c r="D483" t="s">
+        <v>980</v>
+      </c>
+      <c r="E483">
+        <v>464</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-05.xlsx
+++ b/report-2026-06-05.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="1007">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-05T20:59:43+05:30</t>
+    <t>Generated 2026-06-05T21:33:38+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-05T20:57:43+05:30 (2m0s ago)</t>
+    <t>2026-06-05T21:31:38+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -2953,10 +2953,88 @@
     <t>20:57:43.611</t>
   </si>
   <si>
+    <t>2026-06-05T21:00:15.2102188+05:30</t>
+  </si>
+  <si>
+    <t>21:00:15.210</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:02:45.1788768+05:30</t>
+  </si>
+  <si>
+    <t>21:02:45.178</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:05:15.3814061+05:30</t>
+  </si>
+  <si>
+    <t>21:05:15.381</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:07:45.300016+05:30</t>
+  </si>
+  <si>
+    <t>21:07:45.300</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:10:15.1588006+05:30</t>
+  </si>
+  <si>
+    <t>21:10:15.158</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:12:45.1755155+05:30</t>
+  </si>
+  <si>
+    <t>21:12:45.175</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:15:15.3820786+05:30</t>
+  </si>
+  <si>
+    <t>21:15:15.382</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:17:45.173373+05:30</t>
+  </si>
+  <si>
+    <t>21:17:45.173</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:20:15.0701542+05:30</t>
+  </si>
+  <si>
+    <t>21:20:15.070</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:22:45.1181274+05:30</t>
+  </si>
+  <si>
+    <t>21:22:45.118</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:25:15.1030705+05:30</t>
+  </si>
+  <si>
+    <t>21:25:15.103</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:27:45.1993327+05:30</t>
+  </si>
+  <si>
+    <t>21:27:45.199</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:31:38.5883682+05:30</t>
+  </si>
+  <si>
+    <t>21:31:38.588</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-05T20:59:43+05:30</t>
+    <t>2026-06-05T21:33:38+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -3511,7 +3589,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.55</t>
+          <t>10.0.56</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -3556,7 +3634,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-05 20:57:28</t>
+          <t>2026-06-05 21:31:23</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3566,12 +3644,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-05 20:57:28</t>
+          <t>2026-06-05 21:31:23</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0h 0m 5s</t>
+          <t>0h 4m 5s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -3581,7 +3659,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20:59:43</t>
+          <t>21:33:38</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3696,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.55</t>
+          <t>10.0.56</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -3638,17 +3716,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>189224.7</t>
+          <t>106742.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>909</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -3658,7 +3736,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -3673,12 +3751,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-05 20:57:28</t>
+          <t>2026-06-05 21:31:23</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0h 0m 0s</t>
+          <t>0h 2m 15s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -3688,7 +3766,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20:59:43</t>
+          <t>21:33:38</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3885,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-05T20:57:43.611099+05:30</t>
+          <t>2026-06-05T21:31:38.5883682+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3817,7 +3895,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20:57:43.611</t>
+          <t>21:31:38.588</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -12414,6 +12492,216 @@
         </is>
       </c>
       <c r="G243" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>1780673557041</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>21:02:37</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>UZsSL35h</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>1780673557242</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>21:02:37</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>UZsSL35h</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>1780673557870</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>21:02:37</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>MzWfKVKY</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>1780673558082</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>21:02:38</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>MzWfKVKY</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>1780673558780</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>21:02:38</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>O5wGgg3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>1780673558972</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>21:02:38</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>O5wGgg3f</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -30235,18 +30523,512 @@
         <v>43</v>
       </c>
     </row>
+    <row r="482">
+      <c r="A482" s="4">
+        <v>465</v>
+      </c>
+      <c r="B482" s="4" t="s">
+        <v>978</v>
+      </c>
+      <c r="C482" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D482" s="4" t="s">
+        <v>979</v>
+      </c>
+      <c r="E482" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F482" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G482" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H482" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I482" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J482" s="4">
+        <v>0</v>
+      </c>
+      <c r="K482" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L482" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="483">
-      <c r="A483" t="s">
-        <v>978</v>
-      </c>
-      <c r="B483" t="s">
-        <v>979</v>
-      </c>
-      <c r="D483" t="s">
+      <c r="A483" s="4">
+        <v>466</v>
+      </c>
+      <c r="B483" s="4" t="s">
         <v>980</v>
       </c>
-      <c r="E483">
-        <v>464</v>
+      <c r="C483" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D483" s="4" t="s">
+        <v>981</v>
+      </c>
+      <c r="E483" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F483" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G483" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H483" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I483" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J483" s="4">
+        <v>0</v>
+      </c>
+      <c r="K483" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L483" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="4">
+        <v>467</v>
+      </c>
+      <c r="B484" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="C484" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D484" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="E484" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F484" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G484" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H484" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I484" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J484" s="4">
+        <v>0</v>
+      </c>
+      <c r="K484" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L484" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="4">
+        <v>468</v>
+      </c>
+      <c r="B485" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="C485" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D485" s="4" t="s">
+        <v>985</v>
+      </c>
+      <c r="E485" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F485" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G485" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H485" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I485" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J485" s="4">
+        <v>0</v>
+      </c>
+      <c r="K485" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L485" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="4">
+        <v>469</v>
+      </c>
+      <c r="B486" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="C486" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D486" s="4" t="s">
+        <v>987</v>
+      </c>
+      <c r="E486" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F486" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G486" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H486" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I486" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J486" s="4">
+        <v>0</v>
+      </c>
+      <c r="K486" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L486" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="4">
+        <v>470</v>
+      </c>
+      <c r="B487" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="C487" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D487" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="E487" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F487" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G487" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H487" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I487" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J487" s="4">
+        <v>0</v>
+      </c>
+      <c r="K487" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L487" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="4">
+        <v>471</v>
+      </c>
+      <c r="B488" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="C488" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D488" s="4" t="s">
+        <v>991</v>
+      </c>
+      <c r="E488" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F488" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G488" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H488" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I488" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J488" s="4">
+        <v>0</v>
+      </c>
+      <c r="K488" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L488" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="4">
+        <v>472</v>
+      </c>
+      <c r="B489" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="C489" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D489" s="4" t="s">
+        <v>993</v>
+      </c>
+      <c r="E489" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F489" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G489" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H489" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I489" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J489" s="4">
+        <v>0</v>
+      </c>
+      <c r="K489" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L489" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="4">
+        <v>473</v>
+      </c>
+      <c r="B490" s="4" t="s">
+        <v>994</v>
+      </c>
+      <c r="C490" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D490" s="4" t="s">
+        <v>995</v>
+      </c>
+      <c r="E490" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F490" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G490" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H490" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I490" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J490" s="4">
+        <v>0</v>
+      </c>
+      <c r="K490" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L490" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="4">
+        <v>474</v>
+      </c>
+      <c r="B491" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="C491" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D491" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="E491" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F491" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G491" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H491" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I491" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J491" s="4">
+        <v>0</v>
+      </c>
+      <c r="K491" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L491" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="4">
+        <v>475</v>
+      </c>
+      <c r="B492" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="C492" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D492" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="E492" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F492" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G492" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H492" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I492" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J492" s="4">
+        <v>0</v>
+      </c>
+      <c r="K492" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L492" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="4">
+        <v>476</v>
+      </c>
+      <c r="B493" s="4" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C493" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D493" s="4" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E493" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F493" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G493" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H493" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I493" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J493" s="4">
+        <v>0</v>
+      </c>
+      <c r="K493" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L493" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="4">
+        <v>477</v>
+      </c>
+      <c r="B494" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C494" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D494" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E494" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F494" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G494" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H494" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I494" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J494" s="4">
+        <v>0</v>
+      </c>
+      <c r="K494" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L494" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B496" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D496" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E496">
+        <v>477</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-05.xlsx
+++ b/report-2026-06-05.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="1007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="1011">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-05T21:33:38+05:30</t>
+    <t>Generated 2026-06-05T21:42:29+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-05T21:31:38+05:30 (2m0s ago)</t>
+    <t>2026-06-05T21:40:28+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -3031,10 +3031,22 @@
     <t>21:31:38.588</t>
   </si>
   <si>
+    <t>2026-06-05T21:34:10.1649185+05:30</t>
+  </si>
+  <si>
+    <t>21:34:10.164</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:40:28.8736805+05:30</t>
+  </si>
+  <si>
+    <t>21:40:28.873</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-05T21:33:38+05:30</t>
+    <t>2026-06-05T21:42:29+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -3629,12 +3641,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 15s</t>
+          <t>0h 2m 14s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-05 21:31:23</t>
+          <t>2026-06-05 21:40:14</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3644,12 +3656,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-05 21:31:23</t>
+          <t>2026-06-05 21:40:14</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0h 4m 5s</t>
+          <t>0h 4m 22s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -3659,7 +3671,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>21:33:38</t>
+          <t>21:42:29</t>
         </is>
       </c>
     </row>
@@ -3716,17 +3728,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>106742.5</t>
+          <t>239715.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>941</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -3736,7 +3748,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -3751,12 +3763,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-05 21:31:23</t>
+          <t>2026-06-05 21:40:14</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0h 2m 15s</t>
+          <t>0h 2m 22s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -3766,7 +3778,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>21:33:38</t>
+          <t>21:42:29</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3897,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-05T21:31:38.5883682+05:30</t>
+          <t>2026-06-05T21:40:28.8736805+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3895,7 +3907,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21:31:38.588</t>
+          <t>21:40:28.873</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -31017,18 +31029,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="495">
+      <c r="A495" s="4">
+        <v>478</v>
+      </c>
+      <c r="B495" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C495" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D495" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E495" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F495" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G495" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H495" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I495" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J495" s="4">
+        <v>0</v>
+      </c>
+      <c r="K495" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L495" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="496">
-      <c r="A496" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B496" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D496" t="s">
+      <c r="A496" s="4">
+        <v>479</v>
+      </c>
+      <c r="B496" s="4" t="s">
         <v>1006</v>
       </c>
-      <c r="E496">
-        <v>477</v>
+      <c r="C496" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D496" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E496" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F496" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G496" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H496" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I496" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J496" s="4">
+        <v>0</v>
+      </c>
+      <c r="K496" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L496" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B498" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D498" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E498">
+        <v>479</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-05.xlsx
+++ b/report-2026-06-05.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="1011">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="1025">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-05T21:42:29+05:30</t>
+    <t>Generated 2026-06-05T21:58:46+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-05T21:40:28+05:30 (2m0s ago)</t>
+    <t>2026-06-05T21:56:45+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -3043,10 +3043,52 @@
     <t>21:40:28.873</t>
   </si>
   <si>
+    <t>2026-06-05T21:43:00.4055695+05:30</t>
+  </si>
+  <si>
+    <t>21:43:00.405</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:45:30.4514951+05:30</t>
+  </si>
+  <si>
+    <t>21:45:30.451</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:48:00.4344015+05:30</t>
+  </si>
+  <si>
+    <t>21:48:00.434</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:50:30.5209957+05:30</t>
+  </si>
+  <si>
+    <t>21:50:30.520</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:53:00.5040537+05:30</t>
+  </si>
+  <si>
+    <t>21:53:00.504</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:55:30.4711531+05:30</t>
+  </si>
+  <si>
+    <t>21:55:30.471</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:56:45.7294134+05:30</t>
+  </si>
+  <si>
+    <t>21:56:45.729</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-05T21:42:29+05:30</t>
+    <t>2026-06-05T21:58:46+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -3646,7 +3688,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-05 21:40:14</t>
+          <t>2026-06-05 21:56:31</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3656,12 +3698,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-05 21:40:14</t>
+          <t>2026-06-05 21:56:31</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0h 4m 22s</t>
+          <t>0h 0m 53s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -3671,7 +3713,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>21:42:29</t>
+          <t>21:58:46</t>
         </is>
       </c>
     </row>
@@ -3728,17 +3770,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>239715.5</t>
+          <t>130412.9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -3763,12 +3805,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-05 21:40:14</t>
+          <t>2026-06-05 21:56:31</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0h 2m 22s</t>
+          <t>0h 0m 8s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -3778,7 +3820,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>21:42:29</t>
+          <t>21:58:46</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3939,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-05T21:40:28.8736805+05:30</t>
+          <t>2026-06-05T21:56:45.7294134+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3907,7 +3949,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21:40:28.873</t>
+          <t>21:56:45.729</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -31105,18 +31147,284 @@
         <v>43</v>
       </c>
     </row>
+    <row r="497">
+      <c r="A497" s="4">
+        <v>480</v>
+      </c>
+      <c r="B497" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C497" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D497" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E497" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F497" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G497" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H497" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I497" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J497" s="4">
+        <v>0</v>
+      </c>
+      <c r="K497" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L497" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="498">
-      <c r="A498" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B498" t="s">
-        <v>1009</v>
-      </c>
-      <c r="D498" t="s">
+      <c r="A498" s="4">
+        <v>481</v>
+      </c>
+      <c r="B498" s="4" t="s">
         <v>1010</v>
       </c>
-      <c r="E498">
-        <v>479</v>
+      <c r="C498" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D498" s="4" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E498" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F498" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G498" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H498" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I498" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J498" s="4">
+        <v>0</v>
+      </c>
+      <c r="K498" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L498" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="4">
+        <v>482</v>
+      </c>
+      <c r="B499" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C499" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D499" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E499" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F499" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G499" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H499" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I499" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J499" s="4">
+        <v>0</v>
+      </c>
+      <c r="K499" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L499" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="4">
+        <v>483</v>
+      </c>
+      <c r="B500" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C500" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D500" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E500" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F500" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G500" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H500" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I500" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J500" s="4">
+        <v>0</v>
+      </c>
+      <c r="K500" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L500" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="4">
+        <v>484</v>
+      </c>
+      <c r="B501" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C501" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D501" s="4" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E501" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F501" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G501" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H501" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I501" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J501" s="4">
+        <v>0</v>
+      </c>
+      <c r="K501" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L501" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="4">
+        <v>485</v>
+      </c>
+      <c r="B502" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C502" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D502" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E502" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F502" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G502" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H502" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I502" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J502" s="4">
+        <v>0</v>
+      </c>
+      <c r="K502" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L502" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="4">
+        <v>486</v>
+      </c>
+      <c r="B503" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C503" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D503" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E503" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F503" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G503" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H503" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I503" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J503" s="4">
+        <v>0</v>
+      </c>
+      <c r="K503" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L503" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B505" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D505" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E505">
+        <v>486</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-05.xlsx
+++ b/report-2026-06-05.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="1025">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="1029">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-05T21:58:46+05:30</t>
+    <t>Generated 2026-06-05T22:03:19+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-05T21:56:45+05:30 (2m0s ago)</t>
+    <t>2026-06-05T22:01:18+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -3085,10 +3085,22 @@
     <t>21:56:45.729</t>
   </si>
   <si>
+    <t>2026-06-05T21:59:17.1650595+05:30</t>
+  </si>
+  <si>
+    <t>21:59:17.165</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:01:18.9909876+05:30</t>
+  </si>
+  <si>
+    <t>22:01:18.990</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-05T21:58:46+05:30</t>
+    <t>2026-06-05T22:03:19+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -3683,12 +3695,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 14s</t>
+          <t>0h 2m 13s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-05 21:56:31</t>
+          <t>2026-06-05 22:01:05</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3698,12 +3710,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-05 21:56:31</t>
+          <t>2026-06-05 22:01:05</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0h 0m 53s</t>
+          <t>0h 1m 34s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -3713,7 +3725,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>21:58:46</t>
+          <t>22:03:19</t>
         </is>
       </c>
     </row>
@@ -3770,17 +3782,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>130412.9</t>
+          <t>139408.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -3790,7 +3802,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -3805,12 +3817,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-05 21:56:31</t>
+          <t>2026-06-05 22:01:05</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0h 0m 8s</t>
+          <t>0h 0m 24s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -3820,7 +3832,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>21:58:46</t>
+          <t>22:03:19</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-05T21:56:45.7294134+05:30</t>
+          <t>2026-06-05T22:01:18.9909876+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3949,7 +3961,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21:56:45.729</t>
+          <t>22:01:18.990</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -31413,18 +31425,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="504">
+      <c r="A504" s="4">
+        <v>487</v>
+      </c>
+      <c r="B504" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C504" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D504" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E504" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F504" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G504" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H504" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I504" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J504" s="4">
+        <v>0</v>
+      </c>
+      <c r="K504" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L504" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="505">
-      <c r="A505" t="s">
-        <v>1022</v>
-      </c>
-      <c r="B505" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D505" t="s">
+      <c r="A505" s="4">
+        <v>488</v>
+      </c>
+      <c r="B505" s="4" t="s">
         <v>1024</v>
       </c>
-      <c r="E505">
-        <v>486</v>
+      <c r="C505" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D505" s="4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E505" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F505" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G505" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H505" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I505" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J505" s="4">
+        <v>0</v>
+      </c>
+      <c r="K505" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L505" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B507" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D507" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E507">
+        <v>488</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-05.xlsx
+++ b/report-2026-06-05.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="1029">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="1039">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-05T22:03:19+05:30</t>
+    <t>Generated 2026-06-05T22:14:19+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-05T22:01:18+05:30 (2m0s ago)</t>
+    <t>2026-06-05T22:12:18+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -3097,10 +3097,40 @@
     <t>22:01:18.990</t>
   </si>
   <si>
+    <t>2026-06-05T22:03:50.3654485+05:30</t>
+  </si>
+  <si>
+    <t>22:03:50.365</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:06:20.4854107+05:30</t>
+  </si>
+  <si>
+    <t>22:06:20.485</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:08:50.4722438+05:30</t>
+  </si>
+  <si>
+    <t>22:08:50.472</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:10:40.5158681+05:30</t>
+  </si>
+  <si>
+    <t>22:10:40.515</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:11:52.1247295+05:30</t>
+  </si>
+  <si>
+    <t>22:11:52.124</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-05T22:03:19+05:30</t>
+    <t>2026-06-05T22:14:19+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -3695,12 +3725,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 13s</t>
+          <t>0h 2m 14s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-05 22:01:05</t>
+          <t>2026-06-05 22:12:04</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3710,12 +3740,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-05 22:01:05</t>
+          <t>2026-06-05 22:12:04</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0h 1m 34s</t>
+          <t>0h 1m 35s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -3725,7 +3755,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>22:03:19</t>
+          <t>22:14:19</t>
         </is>
       </c>
     </row>
@@ -3782,17 +3812,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>139408.5</t>
+          <t>123833.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -3802,7 +3832,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -3817,12 +3847,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-05 22:01:05</t>
+          <t>2026-06-05 22:12:04</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0h 0m 24s</t>
+          <t>0h 0m 0s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -3832,7 +3862,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>22:03:19</t>
+          <t>22:14:19</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-05T22:01:18.9909876+05:30</t>
+          <t>2026-06-05T22:11:52.1247295+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3961,7 +3991,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22:01:18.990</t>
+          <t>22:11:52.124</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -31501,18 +31531,208 @@
         <v>43</v>
       </c>
     </row>
+    <row r="506">
+      <c r="A506" s="4">
+        <v>489</v>
+      </c>
+      <c r="B506" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C506" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D506" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E506" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F506" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G506" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H506" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I506" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J506" s="4">
+        <v>0</v>
+      </c>
+      <c r="K506" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L506" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="507">
-      <c r="A507" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B507" t="s">
-        <v>1027</v>
-      </c>
-      <c r="D507" t="s">
+      <c r="A507" s="4">
+        <v>490</v>
+      </c>
+      <c r="B507" s="4" t="s">
         <v>1028</v>
       </c>
-      <c r="E507">
-        <v>488</v>
+      <c r="C507" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D507" s="4" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E507" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F507" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G507" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H507" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I507" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J507" s="4">
+        <v>0</v>
+      </c>
+      <c r="K507" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L507" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="4">
+        <v>491</v>
+      </c>
+      <c r="B508" s="4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C508" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D508" s="4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E508" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F508" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G508" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H508" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I508" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J508" s="4">
+        <v>0</v>
+      </c>
+      <c r="K508" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L508" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="4">
+        <v>492</v>
+      </c>
+      <c r="B509" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C509" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D509" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E509" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F509" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G509" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H509" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I509" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J509" s="4">
+        <v>0</v>
+      </c>
+      <c r="K509" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L509" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="4">
+        <v>493</v>
+      </c>
+      <c r="B510" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C510" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D510" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E510" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F510" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G510" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H510" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I510" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J510" s="4">
+        <v>0</v>
+      </c>
+      <c r="K510" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L510" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D512" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E512">
+        <v>493</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-05.xlsx
+++ b/report-2026-06-05.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="1039">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="1041">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-05T22:14:19+05:30</t>
+    <t>Generated 2026-06-05T22:16:47+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-05T22:12:18+05:30 (2m0s ago)</t>
+    <t>2026-06-05T22:14:47+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -3127,10 +3127,16 @@
     <t>22:11:52.124</t>
   </si>
   <si>
+    <t>2026-06-05T22:14:47.3133957+05:30</t>
+  </si>
+  <si>
+    <t>22:14:47.313</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-05T22:14:19+05:30</t>
+    <t>2026-06-05T22:16:47+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -3725,12 +3731,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 14s</t>
+          <t>0h 2m 15s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-05 22:12:04</t>
+          <t>2026-06-05 22:14:31</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3740,12 +3746,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-05 22:12:04</t>
+          <t>2026-06-05 22:14:31</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0h 1m 35s</t>
+          <t>0h 3m 51s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -3755,7 +3761,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>22:14:19</t>
+          <t>22:16:47</t>
         </is>
       </c>
     </row>
@@ -3812,17 +3818,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>123833.5</t>
+          <t>120986.3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -3832,7 +3838,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -3847,12 +3853,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-05 22:12:04</t>
+          <t>2026-06-05 22:14:31</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0h 0m 0s</t>
+          <t>0h 1m 56s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -3862,7 +3868,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>22:14:19</t>
+          <t>22:16:47</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3987,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-05T22:11:52.1247295+05:30</t>
+          <t>2026-06-05T22:14:47.3133957+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3991,7 +3997,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22:11:52.124</t>
+          <t>22:14:47.313</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -12798,6 +12804,76 @@
         </is>
       </c>
       <c r="G249" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>1780677896503</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>22:14:56</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>CPgEkhtd</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>1780677896518</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>22:14:56</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>CPgEkhtd</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -31721,18 +31797,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="512">
-      <c r="A512" t="s">
+    <row r="511">
+      <c r="A511" s="4">
+        <v>494</v>
+      </c>
+      <c r="B511" s="4" t="s">
         <v>1036</v>
       </c>
-      <c r="B512" t="s">
+      <c r="C511" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D511" s="4" t="s">
         <v>1037</v>
       </c>
-      <c r="D512" t="s">
+      <c r="E511" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F511" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G511" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H511" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I511" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J511" s="4">
+        <v>0</v>
+      </c>
+      <c r="K511" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L511" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="s">
         <v>1038</v>
       </c>
-      <c r="E512">
-        <v>493</v>
+      <c r="B513" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D513" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E513">
+        <v>494</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-05.xlsx
+++ b/report-2026-06-05.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="1041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="1061">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-05T22:16:47+05:30</t>
+    <t>Generated 2026-06-05T22:40:39+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-05T22:14:47+05:30 (2m0s ago)</t>
+    <t>2026-06-05T22:38:39+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -3133,10 +3133,70 @@
     <t>22:14:47.313</t>
   </si>
   <si>
+    <t>2026-06-05T22:17:18.7202781+05:30</t>
+  </si>
+  <si>
+    <t>22:17:18.720</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:19:48.9499336+05:30</t>
+  </si>
+  <si>
+    <t>22:19:48.949</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:22:18.8288404+05:30</t>
+  </si>
+  <si>
+    <t>22:22:18.828</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:24:48.8097628+05:30</t>
+  </si>
+  <si>
+    <t>22:24:48.809</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:27:18.8243849+05:30</t>
+  </si>
+  <si>
+    <t>22:27:18.824</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:29:48.8259137+05:30</t>
+  </si>
+  <si>
+    <t>22:29:48.825</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:32:18.9288139+05:30</t>
+  </si>
+  <si>
+    <t>22:32:18.928</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:34:48.8584667+05:30</t>
+  </si>
+  <si>
+    <t>22:34:48.858</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:37:19.100573+05:30</t>
+  </si>
+  <si>
+    <t>22:37:19.100</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:38:39.2679885+05:30</t>
+  </si>
+  <si>
+    <t>22:38:39.267</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-05T22:16:47+05:30</t>
+    <t>2026-06-05T22:40:39+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -3691,7 +3751,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.56</t>
+          <t>10.0.57</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -3736,7 +3796,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-05 22:14:31</t>
+          <t>2026-06-05 22:38:24</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3746,12 +3806,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-05 22:14:31</t>
+          <t>2026-06-05 22:38:24</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0h 3m 51s</t>
+          <t>0h 3m 9s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -3761,7 +3821,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>22:16:47</t>
+          <t>22:40:39</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3858,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.56</t>
+          <t>10.0.57</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -3818,17 +3878,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>367.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>120986.3</t>
+          <t>238983.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>659</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -3838,7 +3898,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -3853,12 +3913,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-05 22:14:31</t>
+          <t>2026-06-05 22:38:24</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0h 1m 56s</t>
+          <t>0h 1m 19s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -3868,7 +3928,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>22:16:47</t>
+          <t>22:40:39</t>
         </is>
       </c>
     </row>
@@ -3987,7 +4047,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-05T22:14:47.3133957+05:30</t>
+          <t>2026-06-05T22:38:39.2679885+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3997,7 +4057,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22:14:47.313</t>
+          <t>22:38:39.267</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -12874,6 +12934,671 @@
         </is>
       </c>
       <c r="G251" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>1780678019856</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>22:16:59</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Ej8eHGtZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>1780678019880</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>22:16:59</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Ej8eHGtZ</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>1780678334366</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>22:22:14</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>eFFgixw7</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>1780678334556</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>22:22:14</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>eFFgixw7</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>1780678335005</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>22:22:15</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>OzrhizXe</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>1780678335161</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>22:22:15</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>2c0udw5g</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>1780678335205</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>22:22:15</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>OzrhizXe</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>1780678335364</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>22:22:15</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>2c0udw5g</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>1780678335434</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>22:22:15</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>wNhJyrAm</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>1780678335633</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>22:22:15</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>wNhJyrAm</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>1780678335658</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>22:22:15</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>KlkRboTx</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <v>1780678335853</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>22:22:15</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>KlkRboTx</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>1780678500065</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>22:25:00</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>s8pW3Lhc</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>1780678500090</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>22:25:00</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>s8pW3Lhc</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>1780678512707</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>22:25:12</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>pNrWQrIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>1780678512910</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>22:25:12</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>pNrWQrIO</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>1780678616924</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>22:26:56</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>assist_closed</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>pNrWQrIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>1780679333157</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>22:38:53</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>KN4Vo59x</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>1780679333172</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>22:38:53</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>KN4Vo59x</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -31835,18 +32560,398 @@
         <v>43</v>
       </c>
     </row>
+    <row r="512">
+      <c r="A512" s="4">
+        <v>495</v>
+      </c>
+      <c r="B512" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C512" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D512" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E512" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F512" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G512" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H512" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I512" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J512" s="4">
+        <v>0</v>
+      </c>
+      <c r="K512" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L512" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="513">
-      <c r="A513" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B513" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D513" t="s">
+      <c r="A513" s="4">
+        <v>496</v>
+      </c>
+      <c r="B513" s="4" t="s">
         <v>1040</v>
       </c>
-      <c r="E513">
-        <v>494</v>
+      <c r="C513" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D513" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E513" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F513" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G513" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H513" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I513" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J513" s="4">
+        <v>0</v>
+      </c>
+      <c r="K513" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L513" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="4">
+        <v>497</v>
+      </c>
+      <c r="B514" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C514" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D514" s="4" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E514" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F514" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G514" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H514" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I514" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J514" s="4">
+        <v>0</v>
+      </c>
+      <c r="K514" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L514" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="4">
+        <v>498</v>
+      </c>
+      <c r="B515" s="4" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C515" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D515" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E515" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F515" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G515" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H515" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I515" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J515" s="4">
+        <v>0</v>
+      </c>
+      <c r="K515" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L515" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="4">
+        <v>499</v>
+      </c>
+      <c r="B516" s="4" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C516" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D516" s="4" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E516" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F516" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G516" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H516" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I516" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J516" s="4">
+        <v>0</v>
+      </c>
+      <c r="K516" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L516" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="4">
+        <v>500</v>
+      </c>
+      <c r="B517" s="4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C517" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D517" s="4" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E517" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F517" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G517" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H517" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I517" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J517" s="4">
+        <v>0</v>
+      </c>
+      <c r="K517" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L517" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="4">
+        <v>501</v>
+      </c>
+      <c r="B518" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C518" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D518" s="4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E518" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F518" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G518" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H518" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I518" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J518" s="4">
+        <v>0</v>
+      </c>
+      <c r="K518" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L518" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="4">
+        <v>502</v>
+      </c>
+      <c r="B519" s="4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C519" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D519" s="4" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E519" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F519" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G519" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H519" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I519" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J519" s="4">
+        <v>0</v>
+      </c>
+      <c r="K519" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L519" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="4">
+        <v>503</v>
+      </c>
+      <c r="B520" s="4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C520" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D520" s="4" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E520" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F520" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G520" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H520" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I520" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J520" s="4">
+        <v>0</v>
+      </c>
+      <c r="K520" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L520" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="4">
+        <v>504</v>
+      </c>
+      <c r="B521" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C521" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D521" s="4" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E521" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F521" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G521" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H521" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I521" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J521" s="4">
+        <v>0</v>
+      </c>
+      <c r="K521" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L521" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B523" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D523" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E523">
+        <v>504</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-05.xlsx
+++ b/report-2026-06-05.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="1061">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="1085">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-05T22:40:39+05:30</t>
+    <t>Generated 2026-06-05T23:38:00+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-05T22:38:39+05:30 (2m0s ago)</t>
+    <t>2026-06-05T23:36:00+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -3193,10 +3193,82 @@
     <t>22:38:39.267</t>
   </si>
   <si>
+    <t>2026-06-05T22:43:40.6409975+05:30</t>
+  </si>
+  <si>
+    <t>22:43:40.640</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:48:40.5770074+05:30</t>
+  </si>
+  <si>
+    <t>22:48:40.577</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:53:40.5110221+05:30</t>
+  </si>
+  <si>
+    <t>22:53:40.511</t>
+  </si>
+  <si>
+    <t>2026-06-05T22:58:40.4678118+05:30</t>
+  </si>
+  <si>
+    <t>22:58:40.467</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:03:40.5249164+05:30</t>
+  </si>
+  <si>
+    <t>23:03:40.524</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:08:40.5267202+05:30</t>
+  </si>
+  <si>
+    <t>23:08:40.526</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:13:40.3804465+05:30</t>
+  </si>
+  <si>
+    <t>23:13:40.380</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:18:40.4671586+05:30</t>
+  </si>
+  <si>
+    <t>23:18:40.467</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:23:40.4934517+05:30</t>
+  </si>
+  <si>
+    <t>23:23:40.493</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:28:40.4222089+05:30</t>
+  </si>
+  <si>
+    <t>23:28:40.422</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:33:40.6503058+05:30</t>
+  </si>
+  <si>
+    <t>23:33:40.650</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:36:00.3431032+05:30</t>
+  </si>
+  <si>
+    <t>23:36:00.343</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-05T22:40:39+05:30</t>
+    <t>2026-06-05T23:38:00+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -3751,7 +3823,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.57</t>
+          <t>10.0.58</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -3791,12 +3863,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 15s</t>
+          <t>0h 2m 14s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-05 22:38:24</t>
+          <t>2026-06-05 23:35:45</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3806,12 +3878,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-05 22:38:24</t>
+          <t>2026-06-05 23:35:45</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0h 3m 9s</t>
+          <t>0h 48m 24s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -3821,7 +3893,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>22:40:39</t>
+          <t>23:38:00</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3930,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.57</t>
+          <t>10.0.58</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -3878,17 +3950,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>367.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>238983.5</t>
+          <t>191631.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -3913,12 +3985,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-05 22:38:24</t>
+          <t>2026-06-05 23:35:45</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0h 1m 19s</t>
+          <t>0h 48m 24s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -3928,7 +4000,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>22:40:39</t>
+          <t>23:38:00</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4119,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-05T22:38:39.2679885+05:30</t>
+          <t>2026-06-05T23:36:00.3431032+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4057,7 +4129,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22:38:39.267</t>
+          <t>23:36:00.343</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -13599,6 +13671,76 @@
         </is>
       </c>
       <c r="G270" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>1780682774411</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>23:36:14</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>oH8Evg9O</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <v>1780682774448</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>23:36:14</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>oH8Evg9O</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -32940,18 +33082,474 @@
         <v>43</v>
       </c>
     </row>
+    <row r="522">
+      <c r="A522" s="4">
+        <v>505</v>
+      </c>
+      <c r="B522" s="4" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C522" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D522" s="4" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E522" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F522" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G522" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H522" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I522" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J522" s="4">
+        <v>0</v>
+      </c>
+      <c r="K522" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L522" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="523">
-      <c r="A523" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B523" t="s">
-        <v>1059</v>
-      </c>
-      <c r="D523" t="s">
+      <c r="A523" s="4">
+        <v>506</v>
+      </c>
+      <c r="B523" s="4" t="s">
         <v>1060</v>
       </c>
-      <c r="E523">
-        <v>504</v>
+      <c r="C523" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D523" s="4" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E523" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F523" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G523" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H523" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I523" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J523" s="4">
+        <v>0</v>
+      </c>
+      <c r="K523" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L523" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="4">
+        <v>507</v>
+      </c>
+      <c r="B524" s="4" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C524" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D524" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E524" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F524" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G524" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H524" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I524" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J524" s="4">
+        <v>0</v>
+      </c>
+      <c r="K524" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L524" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="4">
+        <v>508</v>
+      </c>
+      <c r="B525" s="4" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C525" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D525" s="4" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E525" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F525" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G525" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H525" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I525" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J525" s="4">
+        <v>0</v>
+      </c>
+      <c r="K525" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L525" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="4">
+        <v>509</v>
+      </c>
+      <c r="B526" s="4" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C526" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D526" s="4" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E526" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F526" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G526" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H526" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I526" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J526" s="4">
+        <v>0</v>
+      </c>
+      <c r="K526" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L526" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="4">
+        <v>510</v>
+      </c>
+      <c r="B527" s="4" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C527" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D527" s="4" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E527" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F527" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G527" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H527" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I527" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J527" s="4">
+        <v>0</v>
+      </c>
+      <c r="K527" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L527" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="4">
+        <v>511</v>
+      </c>
+      <c r="B528" s="4" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C528" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D528" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E528" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F528" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G528" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H528" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I528" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J528" s="4">
+        <v>0</v>
+      </c>
+      <c r="K528" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L528" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="4">
+        <v>512</v>
+      </c>
+      <c r="B529" s="4" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C529" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D529" s="4" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E529" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F529" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G529" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H529" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I529" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J529" s="4">
+        <v>0</v>
+      </c>
+      <c r="K529" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L529" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="4">
+        <v>513</v>
+      </c>
+      <c r="B530" s="4" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C530" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D530" s="4" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E530" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F530" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G530" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H530" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I530" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J530" s="4">
+        <v>0</v>
+      </c>
+      <c r="K530" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L530" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="4">
+        <v>514</v>
+      </c>
+      <c r="B531" s="4" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C531" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D531" s="4" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E531" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F531" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G531" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H531" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I531" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J531" s="4">
+        <v>0</v>
+      </c>
+      <c r="K531" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L531" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="4">
+        <v>515</v>
+      </c>
+      <c r="B532" s="4" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C532" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D532" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E532" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F532" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G532" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H532" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I532" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J532" s="4">
+        <v>0</v>
+      </c>
+      <c r="K532" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L532" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="4">
+        <v>516</v>
+      </c>
+      <c r="B533" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C533" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D533" s="4" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E533" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F533" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G533" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H533" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I533" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J533" s="4">
+        <v>0</v>
+      </c>
+      <c r="K533" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L533" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B535" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D535" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E535">
+        <v>516</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-05.xlsx
+++ b/report-2026-06-05.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="1085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="1089">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-05T23:38:00+05:30</t>
+    <t>Generated 2026-06-05T23:46:52+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-05T23:36:00+05:30 (2m0s ago)</t>
+    <t>2026-06-05T23:44:51+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -3265,10 +3265,22 @@
     <t>23:36:00.343</t>
   </si>
   <si>
+    <t>2026-06-05T23:41:01.6842203+05:30</t>
+  </si>
+  <si>
+    <t>23:41:01.684</t>
+  </si>
+  <si>
+    <t>2026-06-05T23:44:51.8225353+05:30</t>
+  </si>
+  <si>
+    <t>23:44:51.822</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-05T23:38:00+05:30</t>
+    <t>2026-06-05T23:46:52+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -3868,7 +3880,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-05 23:35:45</t>
+          <t>2026-06-05 23:44:37</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3878,12 +3890,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-05 23:35:45</t>
+          <t>2026-06-05 23:44:37</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0h 48m 24s</t>
+          <t>0h 56m 49s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -3893,7 +3905,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>23:38:00</t>
+          <t>23:46:52</t>
         </is>
       </c>
     </row>
@@ -3950,17 +3962,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>191631.5</t>
+          <t>238639.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>942</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -3985,12 +3997,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-05 23:35:45</t>
+          <t>2026-06-05 23:44:37</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0h 48m 24s</t>
+          <t>0h 54m 49s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -4000,7 +4012,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>23:38:00</t>
+          <t>23:46:52</t>
         </is>
       </c>
     </row>
@@ -4119,7 +4131,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-05T23:36:00.3431032+05:30</t>
+          <t>2026-06-05T23:44:51.8225353+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4129,7 +4141,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23:36:00.343</t>
+          <t>23:44:51.822</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -33538,18 +33550,94 @@
         <v>43</v>
       </c>
     </row>
+    <row r="534">
+      <c r="A534" s="4">
+        <v>517</v>
+      </c>
+      <c r="B534" s="4" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C534" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D534" s="4" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E534" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F534" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G534" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H534" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I534" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J534" s="4">
+        <v>0</v>
+      </c>
+      <c r="K534" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L534" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
     <row r="535">
-      <c r="A535" t="s">
-        <v>1082</v>
-      </c>
-      <c r="B535" t="s">
-        <v>1083</v>
-      </c>
-      <c r="D535" t="s">
+      <c r="A535" s="4">
+        <v>518</v>
+      </c>
+      <c r="B535" s="4" t="s">
         <v>1084</v>
       </c>
-      <c r="E535">
-        <v>516</v>
+      <c r="C535" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D535" s="4" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E535" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F535" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G535" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H535" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I535" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J535" s="4">
+        <v>0</v>
+      </c>
+      <c r="K535" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L535" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B537" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D537" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E537">
+        <v>518</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-05.xlsx
+++ b/report-2026-06-05.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="1089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="1091">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-05T23:46:52+05:30</t>
+    <t>Generated 2026-06-05T23:50:03+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-05T23:44:51+05:30 (2m0s ago)</t>
+    <t>2026-06-05T23:48:02+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -3277,10 +3277,16 @@
     <t>23:44:51.822</t>
   </si>
   <si>
+    <t>2026-06-05T23:48:02.900954+05:30</t>
+  </si>
+  <si>
+    <t>23:48:02.900</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-05T23:46:52+05:30</t>
+    <t>2026-06-05T23:50:03+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -3880,7 +3886,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-05 23:44:37</t>
+          <t>2026-06-05 23:47:48</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3890,12 +3896,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-05 23:44:37</t>
+          <t>2026-06-05 23:47:48</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0h 56m 49s</t>
+          <t>0h 59m 49s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -3905,7 +3911,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>23:46:52</t>
+          <t>23:50:03</t>
         </is>
       </c>
     </row>
@@ -3962,17 +3968,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>238639.5</t>
+          <t>238659.5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>818</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -3997,12 +4003,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-05 23:44:37</t>
+          <t>2026-06-05 23:47:48</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0h 54m 49s</t>
+          <t>0h 57m 49s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -4012,7 +4018,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>23:46:52</t>
+          <t>23:50:03</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4137,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-05T23:44:51.8225353+05:30</t>
+          <t>2026-06-05T23:48:02.900954+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4141,7 +4147,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23:44:51.822</t>
+          <t>23:48:02.900</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -13753,6 +13759,76 @@
         </is>
       </c>
       <c r="G272" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>1780683489220</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>23:48:09</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>assist_created</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>9CWNCTsI</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>1780683489235</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>23:48:09</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>assist_view</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>9CWNCTsI</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -33626,18 +33702,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="537">
-      <c r="A537" t="s">
+    <row r="536">
+      <c r="A536" s="4">
+        <v>519</v>
+      </c>
+      <c r="B536" s="4" t="s">
         <v>1086</v>
       </c>
-      <c r="B537" t="s">
+      <c r="C536" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D536" s="4" t="s">
         <v>1087</v>
       </c>
-      <c r="D537" t="s">
+      <c r="E536" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F536" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G536" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H536" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I536" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J536" s="4">
+        <v>0</v>
+      </c>
+      <c r="K536" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L536" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="s">
         <v>1088</v>
       </c>
-      <c r="E537">
-        <v>518</v>
+      <c r="B538" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D538" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E538">
+        <v>519</v>
       </c>
     </row>
   </sheetData>
